--- a/apps/web/public/modelos/pedido-cs-2.xlsx
+++ b/apps/web/public/modelos/pedido-cs-2.xlsx
@@ -6197,14 +6197,14 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="25">
-        <v>15</v>
+        <v>2201</v>
       </c>
       <c r="B1" s="51"/>
       <c r="C1" s="52"/>
       <c r="D1" s="52"/>
       <c r="E1" s="53"/>
       <c r="F1" s="6">
-        <v>24.9</v>
+        <v>76.9</v>
       </c>
       <c r="H1" s="23" t="s">
         <v>24</v>
@@ -6215,15 +6215,17 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
-        <v>49</v>
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>2201E</t>
+        </is>
       </c>
       <c r="B2" s="51"/>
       <c r="C2" s="52"/>
       <c r="D2" s="52"/>
       <c r="E2" s="53"/>
       <c r="F2" s="6">
-        <v>26.9</v>
+        <v>84.9</v>
       </c>
       <c r="H2" s="23" t="s">
         <v>25</v>
@@ -6235,70 +6237,72 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="25">
-        <v>70</v>
+        <v>2202</v>
       </c>
       <c r="B3" s="51"/>
       <c r="C3" s="52"/>
       <c r="D3" s="52"/>
       <c r="E3" s="53"/>
       <c r="F3" s="6">
-        <v>42.9</v>
+        <v>65.9</v>
       </c>
       <c r="H3" s="23"/>
       <c r="I3" s="22"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="25" t="s">
-        <v>165</v>
+      <c r="A4" s="25">
+        <v>2203</v>
       </c>
       <c r="B4" s="51"/>
       <c r="C4" s="52"/>
       <c r="D4" s="52"/>
       <c r="E4" s="53"/>
       <c r="F4" s="6">
-        <v>47.9</v>
+        <v>74.9</v>
       </c>
       <c r="H4" s="23"/>
       <c r="I4" s="22"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="25">
-        <v>72</v>
+        <v>2204</v>
       </c>
       <c r="B5" s="51"/>
       <c r="C5" s="52"/>
       <c r="D5" s="52"/>
       <c r="E5" s="53"/>
       <c r="F5" s="6">
-        <v>40.9</v>
+        <v>104.9</v>
       </c>
       <c r="H5" s="23"/>
       <c r="I5" s="22"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="25" t="s">
-        <v>166</v>
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>2204E</t>
+        </is>
       </c>
       <c r="B6" s="51"/>
       <c r="C6" s="52"/>
       <c r="D6" s="52"/>
       <c r="E6" s="53"/>
       <c r="F6" s="6">
-        <v>45</v>
+        <v>109.9</v>
       </c>
       <c r="H6" s="23"/>
       <c r="I6" s="22"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="25">
-        <v>80</v>
+        <v>2205</v>
       </c>
       <c r="B7" s="51"/>
       <c r="C7" s="52"/>
       <c r="D7" s="52"/>
       <c r="E7" s="53"/>
       <c r="F7" s="6">
-        <v>42.9</v>
+        <v>82.9</v>
       </c>
       <c r="H7" s="23" t="s">
         <v>31</v>
@@ -6311,15 +6315,17 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="25" t="s">
-        <v>50</v>
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>2205E</t>
+        </is>
       </c>
       <c r="B8" s="51"/>
       <c r="C8" s="52"/>
       <c r="D8" s="52"/>
       <c r="E8" s="53"/>
-      <c r="F8" s="12">
-        <v>47.9</v>
+      <c r="F8" s="6">
+        <v>90.9</v>
       </c>
       <c r="H8" s="23" t="s">
         <v>26</v>
@@ -6330,14 +6336,14 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="25">
-        <v>83</v>
+        <v>2206</v>
       </c>
       <c r="B9" s="51"/>
       <c r="C9" s="52"/>
       <c r="D9" s="52"/>
       <c r="E9" s="53"/>
       <c r="F9" s="6">
-        <v>40.9</v>
+        <v>92.9</v>
       </c>
       <c r="H9" s="22"/>
       <c r="I9" s="22" t="s">
@@ -6345,15 +6351,15 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="25" t="s">
-        <v>51</v>
+      <c r="A10" s="25">
+        <v>2207</v>
       </c>
       <c r="B10" s="51"/>
       <c r="C10" s="52"/>
       <c r="D10" s="52"/>
       <c r="E10" s="53"/>
       <c r="F10" s="6">
-        <v>43.9</v>
+        <v>63.9</v>
       </c>
       <c r="H10" s="22"/>
       <c r="I10" s="22" t="s">
@@ -6361,15 +6367,17 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="26">
-        <v>85</v>
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>2207E</t>
+        </is>
       </c>
       <c r="B11" s="51"/>
       <c r="C11" s="52"/>
       <c r="D11" s="52"/>
       <c r="E11" s="53"/>
-      <c r="F11" s="32">
-        <v>36.9</v>
+      <c r="F11" s="6">
+        <v>70.9</v>
       </c>
       <c r="H11" s="22"/>
       <c r="I11" s="22" t="s">
@@ -6377,15 +6385,15 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="25" t="s">
-        <v>52</v>
+      <c r="A12" s="25">
+        <v>2208</v>
       </c>
       <c r="B12" s="51"/>
       <c r="C12" s="52"/>
       <c r="D12" s="52"/>
       <c r="E12" s="53"/>
       <c r="F12" s="6">
-        <v>40.9</v>
+        <v>64.9</v>
       </c>
       <c r="H12" s="22"/>
       <c r="I12" s="24" t="s">
@@ -6393,15 +6401,17 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="25">
-        <v>86</v>
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>2208E</t>
+        </is>
       </c>
       <c r="B13" s="51"/>
       <c r="C13" s="52"/>
       <c r="D13" s="52"/>
       <c r="E13" s="53"/>
       <c r="F13" s="6">
-        <v>48.9</v>
+        <v>71.9</v>
       </c>
       <c r="H13" s="22"/>
       <c r="I13" s="24" t="s">
@@ -6409,15 +6419,15 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="25" t="s">
-        <v>53</v>
+      <c r="A14" s="25">
+        <v>2212</v>
       </c>
       <c r="B14" s="51"/>
       <c r="C14" s="52"/>
       <c r="D14" s="52"/>
       <c r="E14" s="53"/>
-      <c r="F14" s="12">
-        <v>53.9</v>
+      <c r="F14" s="6">
+        <v>57.9</v>
       </c>
       <c r="H14" s="22"/>
       <c r="I14" s="24" t="s">
@@ -6426,14 +6436,14 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="25">
-        <v>87</v>
+        <v>2213</v>
       </c>
       <c r="B15" s="51"/>
       <c r="C15" s="52"/>
       <c r="D15" s="52"/>
       <c r="E15" s="53"/>
       <c r="F15" s="6">
-        <v>42.9</v>
+        <v>65.9</v>
       </c>
       <c r="H15" s="22"/>
       <c r="I15" s="22" t="s">
@@ -6441,15 +6451,17 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" s="26" t="s">
-        <v>54</v>
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>2213E</t>
+        </is>
       </c>
       <c r="B16" s="51"/>
       <c r="C16" s="52"/>
       <c r="D16" s="52"/>
       <c r="E16" s="53"/>
-      <c r="F16" s="32">
-        <v>47.9</v>
+      <c r="F16" s="6">
+        <v>72.9</v>
       </c>
       <c r="H16" s="22"/>
       <c r="I16" s="22" t="s">
@@ -6458,14 +6470,14 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="25">
-        <v>88</v>
+        <v>2215</v>
       </c>
       <c r="B17" s="51"/>
       <c r="C17" s="52"/>
       <c r="D17" s="52"/>
       <c r="E17" s="53"/>
       <c r="F17" s="6">
-        <v>44.9</v>
+        <v>78</v>
       </c>
       <c r="H17" s="22"/>
       <c r="I17" s="22" t="s">
@@ -6473,15 +6485,17 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="25" t="s">
-        <v>55</v>
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>2215E</t>
+        </is>
       </c>
       <c r="B18" s="51"/>
       <c r="C18" s="52"/>
       <c r="D18" s="52"/>
       <c r="E18" s="53"/>
       <c r="F18" s="6">
-        <v>49</v>
+        <v>86.9</v>
       </c>
       <c r="H18" s="22"/>
       <c r="I18" s="22" t="s">
@@ -6490,14 +6504,14 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="25">
-        <v>90</v>
+        <v>2216</v>
       </c>
       <c r="B19" s="51"/>
       <c r="C19" s="52"/>
       <c r="D19" s="52"/>
       <c r="E19" s="53"/>
-      <c r="F19" s="12">
-        <v>38.9</v>
+      <c r="F19" s="6">
+        <v>72.9</v>
       </c>
       <c r="H19" s="22"/>
       <c r="I19" s="24" t="s">
@@ -6505,15 +6519,17 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="25" t="s">
-        <v>56</v>
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>2216E</t>
+        </is>
       </c>
       <c r="B20" s="51"/>
       <c r="C20" s="52"/>
       <c r="D20" s="52"/>
       <c r="E20" s="53"/>
       <c r="F20" s="6">
-        <v>42.9</v>
+        <v>79.9</v>
       </c>
       <c r="I20" s="22" t="s">
         <v>42</v>
@@ -6521,211 +6537,225 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="25">
-        <v>91</v>
+        <v>2217</v>
       </c>
       <c r="B21" s="51"/>
       <c r="C21" s="52"/>
       <c r="D21" s="52"/>
       <c r="E21" s="53"/>
       <c r="F21" s="6">
-        <v>41.9</v>
+        <v>72.9</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="25" t="s">
-        <v>57</v>
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>2217E</t>
+        </is>
       </c>
       <c r="B22" s="51"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
       <c r="E22" s="53"/>
       <c r="F22" s="6">
-        <v>45</v>
+        <v>79.9</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="25">
-        <v>92</v>
+        <v>2230</v>
       </c>
       <c r="B23" s="51"/>
       <c r="C23" s="52"/>
       <c r="D23" s="52"/>
       <c r="E23" s="53"/>
-      <c r="F23" s="12">
-        <v>38.9</v>
+      <c r="F23" s="6">
+        <v>84.9</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="25" t="s">
-        <v>58</v>
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>2230E</t>
+        </is>
       </c>
       <c r="B24" s="51"/>
       <c r="C24" s="52"/>
       <c r="D24" s="52"/>
       <c r="E24" s="53"/>
       <c r="F24" s="6">
-        <v>42.9</v>
+        <v>93.9</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="25">
-        <v>93</v>
+        <v>2232</v>
       </c>
       <c r="B25" s="51"/>
       <c r="C25" s="52"/>
       <c r="D25" s="52"/>
       <c r="E25" s="53"/>
-      <c r="F25" s="12">
-        <v>42.9</v>
+      <c r="F25" s="6">
+        <v>69.9</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" s="26" t="s">
-        <v>59</v>
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>2232E</t>
+        </is>
       </c>
       <c r="B26" s="51"/>
       <c r="C26" s="52"/>
       <c r="D26" s="52"/>
       <c r="E26" s="53"/>
-      <c r="F26" s="32">
-        <v>47.9</v>
+      <c r="F26" s="6">
+        <v>76.9</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="25">
-        <v>94</v>
+        <v>2234</v>
       </c>
       <c r="B27" s="51"/>
       <c r="C27" s="52"/>
       <c r="D27" s="52"/>
       <c r="E27" s="53"/>
       <c r="F27" s="6">
-        <v>38.9</v>
+        <v>91.9</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="25" t="s">
-        <v>60</v>
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>2234E</t>
+        </is>
       </c>
       <c r="B28" s="51"/>
       <c r="C28" s="52"/>
       <c r="D28" s="52"/>
       <c r="E28" s="53"/>
-      <c r="F28" s="12">
-        <v>42.9</v>
+      <c r="F28" s="6">
+        <v>96.9</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="25">
-        <v>95</v>
+        <v>2240</v>
       </c>
       <c r="B29" s="51"/>
       <c r="C29" s="52"/>
       <c r="D29" s="52"/>
       <c r="E29" s="53"/>
       <c r="F29" s="6">
-        <v>43.9</v>
+        <v>84.9</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" s="25" t="s">
-        <v>61</v>
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>2240E</t>
+        </is>
       </c>
       <c r="B30" s="51"/>
       <c r="C30" s="52"/>
       <c r="D30" s="52"/>
       <c r="E30" s="53"/>
       <c r="F30" s="6">
-        <v>47.9</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="25">
-        <v>96</v>
+        <v>2244</v>
       </c>
       <c r="B31" s="51"/>
       <c r="C31" s="52"/>
       <c r="D31" s="52"/>
       <c r="E31" s="53"/>
-      <c r="F31" s="32">
-        <v>51.9</v>
+      <c r="F31" s="6">
+        <v>72.9</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" s="26" t="s">
-        <v>62</v>
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>2244E</t>
+        </is>
       </c>
       <c r="B32" s="51"/>
       <c r="C32" s="52"/>
       <c r="D32" s="52"/>
       <c r="E32" s="53"/>
-      <c r="F32" s="32">
-        <v>56.9</v>
+      <c r="F32" s="6">
+        <v>79.9</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" s="26">
-        <v>102</v>
+      <c r="A33" s="25">
+        <v>2246</v>
       </c>
       <c r="B33" s="51"/>
       <c r="C33" s="52"/>
       <c r="D33" s="52"/>
       <c r="E33" s="53"/>
-      <c r="F33" s="32">
-        <v>30.9</v>
+      <c r="F33" s="6">
+        <v>59.9</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="26">
-        <v>103</v>
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>2246E</t>
+        </is>
       </c>
       <c r="B34" s="51"/>
       <c r="C34" s="52"/>
       <c r="D34" s="52"/>
       <c r="E34" s="53"/>
-      <c r="F34" s="32">
-        <v>28.9</v>
+      <c r="F34" s="6">
+        <v>65.9</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="26">
-        <v>104</v>
+      <c r="A35" s="25">
+        <v>2247</v>
       </c>
       <c r="B35" s="51"/>
       <c r="C35" s="52"/>
       <c r="D35" s="52"/>
       <c r="E35" s="53"/>
-      <c r="F35" s="32">
-        <v>28.9</v>
+      <c r="F35" s="6">
+        <v>43.9</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="26">
-        <v>107</v>
+      <c r="A36" s="25">
+        <v>2251</v>
       </c>
       <c r="B36" s="51"/>
       <c r="C36" s="52"/>
       <c r="D36" s="52"/>
       <c r="E36" s="53"/>
-      <c r="F36" s="32">
-        <v>43.9</v>
+      <c r="F36" s="6">
+        <v>36.9</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="26" t="s">
-        <v>190</v>
+      <c r="A37" s="25">
+        <v>2252</v>
       </c>
       <c r="B37" s="51"/>
       <c r="C37" s="52"/>
       <c r="D37" s="52"/>
       <c r="E37" s="53"/>
-      <c r="F37" s="32">
-        <v>48.9</v>
+      <c r="F37" s="6">
+        <v>36.9</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" s="27">
-        <v>108</v>
+      <c r="A38" s="25">
+        <v>2253</v>
       </c>
       <c r="B38" s="51" t="s">
         <v>156</v>
@@ -6733,157 +6763,165 @@
       <c r="C38" s="52"/>
       <c r="D38" s="52"/>
       <c r="E38" s="53"/>
-      <c r="F38" s="32">
-        <v>6.9</v>
+      <c r="F38" s="6">
+        <v>54.9</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" s="26">
-        <v>109</v>
+      <c r="A39" s="25">
+        <v>2254</v>
       </c>
       <c r="B39" s="51"/>
       <c r="C39" s="52"/>
       <c r="D39" s="52"/>
       <c r="E39" s="53"/>
-      <c r="F39" s="32">
-        <v>34</v>
+      <c r="F39" s="6">
+        <v>54.9</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" s="27" t="s">
-        <v>64</v>
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>2254E</t>
+        </is>
       </c>
       <c r="B40" s="51"/>
       <c r="C40" s="52"/>
       <c r="D40" s="52"/>
       <c r="E40" s="53"/>
-      <c r="F40" s="32">
-        <v>36.9</v>
+      <c r="F40" s="6">
+        <v>60.9</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="26">
-        <v>110</v>
+      <c r="A41" s="25">
+        <v>2256</v>
       </c>
       <c r="B41" s="51"/>
       <c r="C41" s="52"/>
       <c r="D41" s="52"/>
       <c r="E41" s="53"/>
-      <c r="F41" s="32">
-        <v>29.9</v>
+      <c r="F41" s="6">
+        <v>42.9</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" s="26" t="s">
-        <v>65</v>
+      <c r="A42" s="25">
+        <v>2257</v>
       </c>
       <c r="B42" s="51"/>
       <c r="C42" s="52"/>
       <c r="D42" s="52"/>
       <c r="E42" s="53"/>
-      <c r="F42" s="32">
-        <v>32.9</v>
+      <c r="F42" s="6">
+        <v>39.9</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" s="26">
-        <v>111</v>
+      <c r="A43" s="25">
+        <v>2258</v>
       </c>
       <c r="B43" s="51"/>
       <c r="C43" s="52"/>
       <c r="D43" s="52"/>
       <c r="E43" s="53"/>
-      <c r="F43" s="32">
-        <v>25.9</v>
+      <c r="F43" s="6">
+        <v>39.9</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" s="26" t="s">
-        <v>66</v>
+      <c r="A44" s="25">
+        <v>2260</v>
       </c>
       <c r="B44" s="51"/>
       <c r="C44" s="52"/>
       <c r="D44" s="52"/>
       <c r="E44" s="53"/>
-      <c r="F44" s="32">
-        <v>27.9</v>
+      <c r="F44" s="6">
+        <v>43.9</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" s="26">
-        <v>113</v>
+      <c r="A45" s="25">
+        <v>2265</v>
       </c>
       <c r="B45" s="51"/>
       <c r="C45" s="52"/>
       <c r="D45" s="52"/>
       <c r="E45" s="53"/>
-      <c r="F45" s="32">
-        <v>29.9</v>
+      <c r="F45" s="6">
+        <v>82.9</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="26">
-        <v>114</v>
+      <c r="A46" s="25" t="inlineStr">
+        <is>
+          <t>2265E</t>
+        </is>
       </c>
       <c r="B46" s="51"/>
       <c r="C46" s="52"/>
       <c r="D46" s="52"/>
       <c r="E46" s="53"/>
-      <c r="F46" s="32">
-        <v>29.9</v>
+      <c r="F46" s="6">
+        <v>86.9</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" s="26">
-        <v>115</v>
+      <c r="A47" s="25">
+        <v>2267</v>
       </c>
       <c r="B47" s="51"/>
       <c r="C47" s="52"/>
       <c r="D47" s="52"/>
       <c r="E47" s="53"/>
-      <c r="F47" s="32">
-        <v>27.9</v>
+      <c r="F47" s="6">
+        <v>54.9</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48" s="26" t="s">
-        <v>67</v>
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>2267E</t>
+        </is>
       </c>
       <c r="B48" s="51"/>
       <c r="C48" s="52"/>
       <c r="D48" s="52"/>
       <c r="E48" s="53"/>
-      <c r="F48" s="32">
-        <v>30.9</v>
+      <c r="F48" s="6">
+        <v>57.9</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" s="26">
-        <v>116</v>
+      <c r="A49" s="25">
+        <v>2270</v>
       </c>
       <c r="B49" s="51"/>
       <c r="C49" s="52"/>
       <c r="D49" s="52"/>
       <c r="E49" s="53"/>
-      <c r="F49" s="32">
-        <v>32.9</v>
+      <c r="F49" s="6">
+        <v>54.9</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50" s="26" t="s">
-        <v>68</v>
+      <c r="A50" s="25" t="inlineStr">
+        <is>
+          <t>2270E</t>
+        </is>
       </c>
       <c r="B50" s="51"/>
       <c r="C50" s="52"/>
       <c r="D50" s="52"/>
       <c r="E50" s="53"/>
-      <c r="F50" s="32">
-        <v>36.9</v>
+      <c r="F50" s="6">
+        <v>58.9</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" s="26">
-        <v>118</v>
+      <c r="A51" s="25">
+        <v>2271</v>
       </c>
       <c r="B51" s="51" t="s">
         <v>156</v>
@@ -6891,13 +6929,15 @@
       <c r="C51" s="52"/>
       <c r="D51" s="52"/>
       <c r="E51" s="53"/>
-      <c r="F51" s="12">
-        <v>16.899999999999999</v>
+      <c r="F51" s="6">
+        <v>65.9</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" s="26">
-        <v>119</v>
+      <c r="A52" s="25" t="inlineStr">
+        <is>
+          <t>2271E</t>
+        </is>
       </c>
       <c r="B52" s="51" t="s">
         <v>156</v>
@@ -6906,12 +6946,12 @@
       <c r="D52" s="52"/>
       <c r="E52" s="53"/>
       <c r="F52" s="6">
-        <v>19.899999999999999</v>
+        <v>72.9</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="25">
-        <v>121</v>
+        <v>2278</v>
       </c>
       <c r="B53" s="51" t="s">
         <v>156</v>
@@ -6919,637 +6959,675 @@
       <c r="C53" s="52"/>
       <c r="D53" s="52"/>
       <c r="E53" s="53"/>
-      <c r="F53" s="32">
-        <v>14.9</v>
+      <c r="F53" s="6">
+        <v>72.9</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" s="25">
-        <v>122</v>
+      <c r="A54" s="25" t="inlineStr">
+        <is>
+          <t>2278E</t>
+        </is>
       </c>
       <c r="B54" s="51"/>
       <c r="C54" s="52"/>
       <c r="D54" s="52"/>
       <c r="E54" s="53"/>
-      <c r="F54" s="32">
-        <v>32.9</v>
+      <c r="F54" s="6">
+        <v>76.9</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" s="26" t="s">
-        <v>157</v>
+      <c r="A55" s="25">
+        <v>2279</v>
       </c>
       <c r="B55" s="51"/>
       <c r="C55" s="52"/>
       <c r="D55" s="52"/>
       <c r="E55" s="53"/>
-      <c r="F55" s="32">
-        <v>36.9</v>
+      <c r="F55" s="6">
+        <v>72.9</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" s="26">
-        <v>123</v>
+      <c r="A56" s="25" t="inlineStr">
+        <is>
+          <t>2279E</t>
+        </is>
       </c>
       <c r="B56" s="51"/>
       <c r="C56" s="52"/>
       <c r="D56" s="52"/>
       <c r="E56" s="53"/>
-      <c r="F56" s="32">
-        <v>42.9</v>
+      <c r="F56" s="6">
+        <v>79.9</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" s="25" t="s">
-        <v>69</v>
+      <c r="A57" s="25">
+        <v>2280</v>
       </c>
       <c r="B57" s="51"/>
       <c r="C57" s="52"/>
       <c r="D57" s="52"/>
       <c r="E57" s="53"/>
-      <c r="F57" s="32">
-        <v>47.9</v>
+      <c r="F57" s="6">
+        <v>87.9</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" s="26">
-        <v>124</v>
+      <c r="A58" s="25" t="inlineStr">
+        <is>
+          <t>2280E</t>
+        </is>
       </c>
       <c r="B58" s="51"/>
       <c r="C58" s="52"/>
       <c r="D58" s="52"/>
       <c r="E58" s="53"/>
       <c r="F58" s="6">
-        <v>21.9</v>
+        <v>93.9</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" s="26">
-        <v>125</v>
+      <c r="A59" s="25">
+        <v>2281</v>
       </c>
       <c r="B59" s="51"/>
       <c r="C59" s="52"/>
       <c r="D59" s="52"/>
       <c r="E59" s="53"/>
-      <c r="F59" s="32">
-        <v>43.9</v>
+      <c r="F59" s="6">
+        <v>87.9</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" s="26" t="s">
-        <v>70</v>
+      <c r="A60" s="25" t="inlineStr">
+        <is>
+          <t>2281E</t>
+        </is>
       </c>
       <c r="B60" s="51"/>
       <c r="C60" s="52"/>
       <c r="D60" s="52"/>
       <c r="E60" s="53"/>
-      <c r="F60" s="12">
-        <v>47.9</v>
+      <c r="F60" s="6">
+        <v>94.9</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" s="26">
-        <v>126</v>
+      <c r="A61" s="25">
+        <v>2282</v>
       </c>
       <c r="B61" s="51"/>
       <c r="C61" s="52"/>
       <c r="D61" s="52"/>
       <c r="E61" s="53"/>
       <c r="F61" s="6">
-        <v>41.9</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" s="26" t="s">
-        <v>71</v>
+      <c r="A62" s="25">
+        <v>2283</v>
       </c>
       <c r="B62" s="51"/>
       <c r="C62" s="52"/>
       <c r="D62" s="52"/>
       <c r="E62" s="53"/>
-      <c r="F62" s="12">
-        <v>46.9</v>
+      <c r="F62" s="6">
+        <v>61.9</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="25">
-        <v>128</v>
+        <v>2284</v>
       </c>
       <c r="B63" s="51"/>
       <c r="C63" s="52"/>
       <c r="D63" s="52"/>
       <c r="E63" s="53"/>
-      <c r="F63" s="32">
-        <v>42.9</v>
+      <c r="F63" s="6">
+        <v>127.9</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" s="26" t="s">
-        <v>72</v>
+      <c r="A64" s="25" t="inlineStr">
+        <is>
+          <t>2284E</t>
+        </is>
       </c>
       <c r="B64" s="51"/>
       <c r="C64" s="52"/>
       <c r="D64" s="52"/>
       <c r="E64" s="53"/>
       <c r="F64" s="6">
-        <v>45.9</v>
+        <v>134.9</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="25">
-        <v>129</v>
+        <v>2285</v>
       </c>
       <c r="B65" s="51"/>
       <c r="C65" s="52"/>
       <c r="D65" s="52"/>
       <c r="E65" s="53"/>
-      <c r="F65" s="32">
-        <v>45.9</v>
+      <c r="F65" s="6">
+        <v>106.9</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" s="25" t="s">
-        <v>73</v>
+      <c r="A66" s="25" t="inlineStr">
+        <is>
+          <t>2285E</t>
+        </is>
       </c>
       <c r="B66" s="51"/>
       <c r="C66" s="52"/>
       <c r="D66" s="52"/>
       <c r="E66" s="53"/>
-      <c r="F66" s="32">
-        <v>49.9</v>
+      <c r="F66" s="6">
+        <v>112.9</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="25">
-        <v>130</v>
+        <v>2286</v>
       </c>
       <c r="B67" s="51"/>
       <c r="C67" s="52"/>
       <c r="D67" s="52"/>
       <c r="E67" s="53"/>
-      <c r="F67" s="32">
-        <v>48.9</v>
+      <c r="F67" s="6">
+        <v>59.9</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A68" s="27" t="s">
-        <v>74</v>
+      <c r="A68" s="25" t="inlineStr">
+        <is>
+          <t>2286E</t>
+        </is>
       </c>
       <c r="B68" s="51"/>
       <c r="C68" s="52"/>
       <c r="D68" s="52"/>
       <c r="E68" s="53"/>
-      <c r="F68" s="32">
-        <v>59.9</v>
+      <c r="F68" s="6">
+        <v>65.9</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="25">
-        <v>131</v>
+        <v>2287</v>
       </c>
       <c r="B69" s="51"/>
       <c r="C69" s="52"/>
       <c r="D69" s="52"/>
       <c r="E69" s="53"/>
-      <c r="F69" s="12">
-        <v>16.899999999999999</v>
+      <c r="F69" s="6">
+        <v>32.9</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A70" s="27" t="s">
-        <v>75</v>
+      <c r="A70" s="25" t="inlineStr">
+        <is>
+          <t>2287E</t>
+        </is>
       </c>
       <c r="B70" s="51"/>
       <c r="C70" s="52"/>
       <c r="D70" s="52"/>
       <c r="E70" s="53"/>
-      <c r="F70" s="12">
-        <v>18.899999999999999</v>
+      <c r="F70" s="6">
+        <v>36.9</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A71" s="26">
-        <v>135</v>
+      <c r="A71" s="25">
+        <v>2288</v>
       </c>
       <c r="B71" s="51"/>
       <c r="C71" s="52"/>
       <c r="D71" s="52"/>
       <c r="E71" s="53"/>
-      <c r="F71" s="12">
-        <v>16.899999999999999</v>
+      <c r="F71" s="6">
+        <v>28.9</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A72" s="26" t="s">
-        <v>76</v>
+      <c r="A72" s="25" t="inlineStr">
+        <is>
+          <t>2288E</t>
+        </is>
       </c>
       <c r="B72" s="51"/>
       <c r="C72" s="52"/>
       <c r="D72" s="52"/>
       <c r="E72" s="53"/>
-      <c r="F72" s="32">
-        <v>18.899999999999999</v>
+      <c r="F72" s="6">
+        <v>31.9</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A73" s="26">
-        <v>139</v>
+      <c r="A73" s="25">
+        <v>2289</v>
       </c>
       <c r="B73" s="51"/>
       <c r="C73" s="52"/>
       <c r="D73" s="52"/>
       <c r="E73" s="53"/>
-      <c r="F73" s="32">
-        <v>25.9</v>
+      <c r="F73" s="6">
+        <v>84.9</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A74" s="25">
-        <v>140</v>
+      <c r="A74" s="25" t="inlineStr">
+        <is>
+          <t>2289E</t>
+        </is>
       </c>
       <c r="B74" s="51"/>
       <c r="C74" s="52"/>
       <c r="D74" s="52"/>
       <c r="E74" s="53"/>
-      <c r="F74" s="12">
-        <v>47.9</v>
+      <c r="F74" s="6">
+        <v>93.9</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A75" s="25" t="s">
-        <v>77</v>
+      <c r="A75" s="25">
+        <v>2290</v>
       </c>
       <c r="B75" s="51"/>
       <c r="C75" s="52"/>
       <c r="D75" s="52"/>
       <c r="E75" s="53"/>
-      <c r="F75" s="32">
-        <v>51.9</v>
+      <c r="F75" s="6">
+        <v>76.9</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A76" s="25">
-        <v>141</v>
+      <c r="A76" s="25" t="inlineStr">
+        <is>
+          <t>2290E</t>
+        </is>
       </c>
       <c r="B76" s="51"/>
       <c r="C76" s="52"/>
       <c r="D76" s="52"/>
       <c r="E76" s="53"/>
-      <c r="F76" s="32">
-        <v>38.9</v>
+      <c r="F76" s="6">
+        <v>80.9</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="25">
-        <v>142</v>
+        <v>2291</v>
       </c>
       <c r="B77" s="51"/>
       <c r="C77" s="52"/>
       <c r="D77" s="52"/>
       <c r="E77" s="53"/>
-      <c r="F77" s="12">
-        <v>31.9</v>
+      <c r="F77" s="6">
+        <v>98.9</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A78" s="26">
-        <v>143</v>
+      <c r="A78" s="25" t="inlineStr">
+        <is>
+          <t>2291E</t>
+        </is>
       </c>
       <c r="B78" s="51"/>
       <c r="C78" s="52"/>
       <c r="D78" s="52"/>
       <c r="E78" s="53"/>
       <c r="F78" s="6">
-        <v>31.9</v>
+        <v>104.9</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A79" s="26">
-        <v>145</v>
+      <c r="A79" s="25">
+        <v>2293</v>
       </c>
       <c r="B79" s="51"/>
       <c r="C79" s="52"/>
       <c r="D79" s="52"/>
       <c r="E79" s="53"/>
-      <c r="F79" s="12">
-        <v>54.9</v>
+      <c r="F79" s="6">
+        <v>137.9</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A80" s="26" t="s">
-        <v>78</v>
+      <c r="A80" s="25">
+        <v>2294</v>
       </c>
       <c r="B80" s="51"/>
       <c r="C80" s="52"/>
       <c r="D80" s="52"/>
       <c r="E80" s="53"/>
-      <c r="F80" s="12">
-        <v>58.9</v>
+      <c r="F80" s="6">
+        <v>72.9</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A81" s="26">
-        <v>159</v>
+      <c r="A81" s="25" t="inlineStr">
+        <is>
+          <t>2294E</t>
+        </is>
       </c>
       <c r="B81" s="51"/>
       <c r="C81" s="52"/>
       <c r="D81" s="52"/>
       <c r="E81" s="53"/>
       <c r="F81" s="6">
-        <v>79.900000000000006</v>
+        <v>79.9</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A82" s="26" t="s">
-        <v>79</v>
+      <c r="A82" s="25">
+        <v>2295</v>
       </c>
       <c r="B82" s="51"/>
       <c r="C82" s="52"/>
       <c r="D82" s="52"/>
       <c r="E82" s="53"/>
       <c r="F82" s="6">
-        <v>86.9</v>
+        <v>76.9</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A83" s="26">
-        <v>160</v>
+      <c r="A83" s="25" t="inlineStr">
+        <is>
+          <t>2295E</t>
+        </is>
       </c>
       <c r="B83" s="51"/>
       <c r="C83" s="52"/>
       <c r="D83" s="52"/>
       <c r="E83" s="53"/>
       <c r="F83" s="6">
-        <v>75.900000000000006</v>
+        <v>84.9</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A84" s="25" t="s">
-        <v>80</v>
+      <c r="A84" s="25">
+        <v>2296</v>
       </c>
       <c r="B84" s="51"/>
       <c r="C84" s="52"/>
       <c r="D84" s="52"/>
       <c r="E84" s="53"/>
       <c r="F84" s="6">
-        <v>82</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A85" s="25">
-        <v>161</v>
+      <c r="A85" s="25" t="inlineStr">
+        <is>
+          <t>2296E</t>
+        </is>
       </c>
       <c r="B85" s="51"/>
       <c r="C85" s="52"/>
       <c r="D85" s="52"/>
       <c r="E85" s="53"/>
       <c r="F85" s="6">
-        <v>83.9</v>
+        <v>69.9</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A86" s="25" t="s">
-        <v>81</v>
+      <c r="A86" s="25">
+        <v>22106</v>
       </c>
       <c r="B86" s="51"/>
       <c r="C86" s="52"/>
       <c r="D86" s="52"/>
       <c r="E86" s="53"/>
       <c r="F86" s="6">
-        <v>91.9</v>
+        <v>65.9</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A87" s="25">
-        <v>162</v>
+      <c r="A87" s="25" t="inlineStr">
+        <is>
+          <t>22106E</t>
+        </is>
       </c>
       <c r="B87" s="51"/>
       <c r="C87" s="52"/>
       <c r="D87" s="52"/>
       <c r="E87" s="53"/>
       <c r="F87" s="6">
-        <v>50.9</v>
+        <v>72.9</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="25">
-        <v>163</v>
+        <v>22111</v>
       </c>
       <c r="B88" s="51"/>
       <c r="C88" s="52"/>
       <c r="D88" s="52"/>
       <c r="E88" s="53"/>
       <c r="F88" s="6">
-        <v>50.9</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="25">
-        <v>169</v>
+        <v>22112</v>
       </c>
       <c r="B89" s="51"/>
       <c r="C89" s="52"/>
       <c r="D89" s="52"/>
       <c r="E89" s="53"/>
       <c r="F89" s="6">
-        <v>84.9</v>
+        <v>72.9</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A90" s="25" t="s">
-        <v>163</v>
+      <c r="A90" s="25">
+        <v>22113</v>
       </c>
       <c r="B90" s="51"/>
       <c r="C90" s="52"/>
       <c r="D90" s="52"/>
       <c r="E90" s="53"/>
       <c r="F90" s="6">
-        <v>93</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="25">
-        <v>171</v>
+        <v>22114</v>
       </c>
       <c r="B91" s="51"/>
       <c r="C91" s="52"/>
       <c r="D91" s="52"/>
       <c r="E91" s="53"/>
-      <c r="F91" s="12">
-        <v>87.9</v>
+      <c r="F91" s="6">
+        <v>82.9</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A92" s="25" t="s">
-        <v>82</v>
+      <c r="A92" s="25">
+        <v>22115</v>
       </c>
       <c r="B92" s="51"/>
       <c r="C92" s="52"/>
       <c r="D92" s="52"/>
       <c r="E92" s="53"/>
-      <c r="F92" s="12">
-        <v>96.9</v>
+      <c r="F92" s="6">
+        <v>87.9</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A93" s="25">
-        <v>172</v>
+      <c r="A93" s="25" t="inlineStr">
+        <is>
+          <t>22115E</t>
+        </is>
       </c>
       <c r="B93" s="51"/>
       <c r="C93" s="52"/>
       <c r="D93" s="52"/>
       <c r="E93" s="53"/>
       <c r="F93" s="6">
-        <v>95.9</v>
+        <v>96.9</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A94" s="25" t="s">
-        <v>83</v>
+      <c r="A94" s="25">
+        <v>22116</v>
       </c>
       <c r="B94" s="51"/>
       <c r="C94" s="52"/>
       <c r="D94" s="52"/>
       <c r="E94" s="53"/>
       <c r="F94" s="6">
-        <v>101.9</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A95" s="25">
-        <v>179</v>
+      <c r="A95" s="25" t="inlineStr">
+        <is>
+          <t>22116E</t>
+        </is>
       </c>
       <c r="B95" s="51"/>
       <c r="C95" s="52"/>
       <c r="D95" s="52"/>
       <c r="E95" s="53"/>
       <c r="F95" s="6">
-        <v>54.9</v>
+        <v>70.9</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="25">
-        <v>199</v>
+        <v>22119</v>
       </c>
       <c r="B96" s="51"/>
       <c r="C96" s="52"/>
       <c r="D96" s="52"/>
       <c r="E96" s="53"/>
-      <c r="F96" s="32">
-        <v>80.900000000000006</v>
+      <c r="F96" s="6">
+        <v>76.9</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A97" s="25" t="s">
-        <v>85</v>
+      <c r="A97" s="25">
+        <v>22120</v>
       </c>
       <c r="B97" s="51"/>
       <c r="C97" s="52"/>
       <c r="D97" s="52"/>
       <c r="E97" s="53"/>
       <c r="F97" s="6">
-        <v>87.9</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="25">
-        <v>200</v>
+        <v>22121</v>
       </c>
       <c r="B98" s="51"/>
       <c r="C98" s="52"/>
       <c r="D98" s="52"/>
       <c r="E98" s="53"/>
       <c r="F98" s="6">
-        <v>95.9</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A99" s="25" t="s">
-        <v>86</v>
+      <c r="A99" s="25">
+        <v>22122</v>
       </c>
       <c r="B99" s="51"/>
       <c r="C99" s="52"/>
       <c r="D99" s="52"/>
       <c r="E99" s="53"/>
       <c r="F99" s="6">
-        <v>105.9</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="25">
-        <v>201</v>
+        <v>22126</v>
       </c>
       <c r="B100" s="51"/>
       <c r="C100" s="52"/>
       <c r="D100" s="52"/>
       <c r="E100" s="53"/>
       <c r="F100" s="6">
-        <v>54.9</v>
+        <v>64.9</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="25">
-        <v>202</v>
+        <v>22127</v>
       </c>
       <c r="B101" s="51"/>
       <c r="C101" s="52"/>
       <c r="D101" s="52"/>
       <c r="E101" s="53"/>
       <c r="F101" s="6">
-        <v>70.900000000000006</v>
+        <v>64.9</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="25">
-        <v>203</v>
+        <v>22128</v>
       </c>
       <c r="B102" s="51"/>
       <c r="C102" s="52"/>
       <c r="D102" s="52"/>
       <c r="E102" s="53"/>
-      <c r="F102" s="32">
-        <v>23</v>
+      <c r="F102" s="6">
+        <v>60.9</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="25">
-        <v>204</v>
+        <v>22129</v>
       </c>
       <c r="B103" s="51"/>
       <c r="C103" s="52"/>
       <c r="D103" s="52"/>
       <c r="E103" s="53"/>
-      <c r="F103" s="12">
-        <v>70.900000000000006</v>
+      <c r="F103" s="6">
+        <v>60.9</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A104" s="25">
-        <v>216</v>
+      <c r="A104" s="25" t="inlineStr">
+        <is>
+          <t>22129E</t>
+        </is>
       </c>
       <c r="B104" s="51"/>
       <c r="C104" s="52"/>
       <c r="D104" s="52"/>
       <c r="E104" s="53"/>
       <c r="F104" s="6">
-        <v>32.9</v>
+        <v>66.9</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A105" s="26" t="s">
-        <v>87</v>
+      <c r="A105" s="25">
+        <v>22130</v>
       </c>
       <c r="B105" s="51"/>
       <c r="C105" s="52"/>
       <c r="D105" s="52"/>
       <c r="E105" s="53"/>
       <c r="F105" s="6">
-        <v>35.9</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="25">
-        <v>219</v>
+        <v>22133</v>
       </c>
       <c r="B106" s="51" t="s">
         <v>156</v>
@@ -7558,3637 +7636,2646 @@
       <c r="D106" s="52"/>
       <c r="E106" s="53"/>
       <c r="F106" s="6">
-        <v>17.899999999999999</v>
+        <v>93.9</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A107" s="25">
-        <v>220</v>
+      <c r="A107" s="25" t="inlineStr">
+        <is>
+          <t>22133E</t>
+        </is>
       </c>
       <c r="B107" s="51"/>
       <c r="C107" s="52"/>
       <c r="D107" s="52"/>
       <c r="E107" s="53"/>
       <c r="F107" s="6">
-        <v>60.9</v>
+        <v>102.9</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A108" s="25" t="s">
-        <v>159</v>
+      <c r="A108" s="25">
+        <v>22142</v>
       </c>
       <c r="B108" s="51"/>
       <c r="C108" s="52"/>
       <c r="D108" s="52"/>
       <c r="E108" s="53"/>
       <c r="F108" s="6">
-        <v>65.900000000000006</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="25">
-        <v>221</v>
+        <v>22144</v>
       </c>
       <c r="B109" s="51"/>
       <c r="C109" s="52"/>
       <c r="D109" s="52"/>
       <c r="E109" s="53"/>
       <c r="F109" s="6">
-        <v>60.9</v>
+        <v>65.9</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A110" s="25" t="s">
-        <v>160</v>
+      <c r="A110" s="25">
+        <v>22145</v>
       </c>
       <c r="B110" s="51"/>
       <c r="C110" s="52"/>
       <c r="D110" s="52"/>
       <c r="E110" s="53"/>
       <c r="F110" s="6">
-        <v>65.900000000000006</v>
+        <v>75.9</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="25">
-        <v>222</v>
+        <v>22146</v>
       </c>
       <c r="B111" s="51"/>
       <c r="C111" s="52"/>
       <c r="D111" s="52"/>
       <c r="E111" s="53"/>
       <c r="F111" s="6">
-        <v>54.9</v>
+        <v>98.9</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A112" s="25" t="s">
-        <v>161</v>
+      <c r="A112" s="25">
+        <v>22147</v>
       </c>
       <c r="B112" s="51"/>
       <c r="C112" s="52"/>
       <c r="D112" s="52"/>
       <c r="E112" s="53"/>
       <c r="F112" s="6">
-        <v>60.9</v>
+        <v>76.9</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A113" s="25">
-        <v>223</v>
+      <c r="A113" s="25" t="inlineStr">
+        <is>
+          <t>22147E</t>
+        </is>
       </c>
       <c r="B113" s="51"/>
       <c r="C113" s="52"/>
       <c r="D113" s="52"/>
       <c r="E113" s="53"/>
       <c r="F113" s="6">
-        <v>54.9</v>
+        <v>84.9</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A114" s="25" t="s">
-        <v>162</v>
+      <c r="A114" s="25">
+        <v>22148</v>
       </c>
       <c r="B114" s="51"/>
       <c r="C114" s="52"/>
       <c r="D114" s="52"/>
       <c r="E114" s="53"/>
       <c r="F114" s="6">
-        <v>60.9</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="25">
-        <v>239</v>
+        <v>22149</v>
       </c>
       <c r="B115" s="51"/>
       <c r="C115" s="52"/>
       <c r="D115" s="52"/>
       <c r="E115" s="53"/>
       <c r="F115" s="6">
-        <v>21.9</v>
+        <v>71.9</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="25">
-        <v>240</v>
+        <v>22150</v>
       </c>
       <c r="B116" s="51"/>
       <c r="C116" s="52"/>
       <c r="D116" s="52"/>
       <c r="E116" s="53"/>
       <c r="F116" s="6">
-        <v>53.9</v>
+        <v>65.9</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A117" s="25" t="s">
-        <v>88</v>
+      <c r="A117" s="25">
+        <v>22151</v>
       </c>
       <c r="B117" s="51"/>
       <c r="C117" s="52"/>
       <c r="D117" s="52"/>
       <c r="E117" s="53"/>
       <c r="F117" s="6">
-        <v>58.9</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="25">
-        <v>242</v>
+        <v>22152</v>
       </c>
       <c r="B118" s="51"/>
       <c r="C118" s="52"/>
       <c r="D118" s="52"/>
       <c r="E118" s="53"/>
-      <c r="F118" s="32">
-        <v>35.9</v>
+      <c r="F118" s="6">
+        <v>42.9</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A119" s="26">
-        <v>245</v>
+      <c r="A119" s="25">
+        <v>22153</v>
       </c>
       <c r="B119" s="51"/>
       <c r="C119" s="52"/>
       <c r="D119" s="52"/>
       <c r="E119" s="53"/>
-      <c r="F119" s="12">
-        <v>48.9</v>
+      <c r="F119" s="6">
+        <v>71.9</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A120" s="25" t="s">
-        <v>89</v>
+      <c r="A120" s="25">
+        <v>22154</v>
       </c>
       <c r="B120" s="51"/>
       <c r="C120" s="52"/>
       <c r="D120" s="52"/>
       <c r="E120" s="53"/>
       <c r="F120" s="6">
-        <v>53.9</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="25">
-        <v>250</v>
+        <v>22155</v>
       </c>
       <c r="B121" s="51"/>
       <c r="C121" s="52"/>
       <c r="D121" s="52"/>
       <c r="E121" s="53"/>
-      <c r="F121" s="32">
-        <v>48.9</v>
+      <c r="F121" s="6">
+        <v>47.9</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="25">
-        <v>260</v>
+        <v>22156</v>
       </c>
       <c r="B122" s="51"/>
       <c r="C122" s="52"/>
       <c r="D122" s="52"/>
       <c r="E122" s="53"/>
-      <c r="F122" s="32">
-        <v>53.9</v>
+      <c r="F122" s="6">
+        <v>76.9</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A123" s="25" t="s">
-        <v>164</v>
+      <c r="A123" s="25">
+        <v>22157</v>
       </c>
       <c r="B123" s="51"/>
       <c r="C123" s="52"/>
       <c r="D123" s="52"/>
       <c r="E123" s="53"/>
-      <c r="F123" s="32">
-        <v>58.9</v>
+      <c r="F123" s="6">
+        <v>60.9</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="25">
-        <v>262</v>
+        <v>22158</v>
       </c>
       <c r="B124" s="51"/>
       <c r="C124" s="52"/>
       <c r="D124" s="52"/>
       <c r="E124" s="53"/>
-      <c r="F124" s="32">
-        <v>53.9</v>
+      <c r="F124" s="6">
+        <v>36.9</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" s="25">
-        <v>263</v>
+        <v>22159</v>
       </c>
       <c r="B125" s="51"/>
       <c r="C125" s="52"/>
       <c r="D125" s="52"/>
       <c r="E125" s="53"/>
-      <c r="F125" s="32">
-        <v>53.9</v>
+      <c r="F125" s="6">
+        <v>43.9</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" s="25">
-        <v>300</v>
+        <v>22160</v>
       </c>
       <c r="B126" s="51"/>
       <c r="C126" s="52"/>
       <c r="D126" s="52"/>
       <c r="E126" s="53"/>
       <c r="F126" s="6">
-        <v>36.9</v>
+        <v>109.9</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" s="25">
-        <v>301</v>
+        <v>22161</v>
       </c>
       <c r="B127" s="51"/>
       <c r="C127" s="52"/>
       <c r="D127" s="52"/>
       <c r="E127" s="53"/>
       <c r="F127" s="6">
-        <v>49.9</v>
+        <v>91.9</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A128" s="25" t="s">
-        <v>158</v>
+      <c r="A128" s="25">
+        <v>22162</v>
       </c>
       <c r="B128" s="51"/>
       <c r="C128" s="52"/>
       <c r="D128" s="52"/>
       <c r="E128" s="53"/>
       <c r="F128" s="6">
-        <v>53.9</v>
+        <v>71.9</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" s="25">
-        <v>303</v>
+        <v>22163</v>
       </c>
       <c r="B129" s="51"/>
       <c r="C129" s="52"/>
       <c r="D129" s="52"/>
       <c r="E129" s="53"/>
-      <c r="F129" s="32">
-        <v>35.9</v>
+      <c r="F129" s="6">
+        <v>91.9</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" s="25">
-        <v>304</v>
+        <v>22164</v>
       </c>
       <c r="B130" s="51"/>
       <c r="C130" s="52"/>
       <c r="D130" s="52"/>
       <c r="E130" s="53"/>
-      <c r="F130" s="32">
-        <v>45</v>
+      <c r="F130" s="6">
+        <v>87.9</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A131" s="25" t="s">
-        <v>167</v>
+      <c r="A131" s="25">
+        <v>22165</v>
       </c>
       <c r="B131" s="51"/>
       <c r="C131" s="52"/>
       <c r="D131" s="52"/>
       <c r="E131" s="53"/>
-      <c r="F131" s="32">
-        <v>49.9</v>
+      <c r="F131" s="6">
+        <v>98.9</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" s="25">
-        <v>305</v>
+        <v>22166</v>
       </c>
       <c r="B132" s="51"/>
       <c r="C132" s="52"/>
       <c r="D132" s="52"/>
       <c r="E132" s="53"/>
-      <c r="F132" s="32">
-        <v>32.9</v>
+      <c r="F132" s="6">
+        <v>51.9</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" s="25">
-        <v>306</v>
+        <v>22167</v>
       </c>
       <c r="B133" s="51"/>
       <c r="C133" s="52"/>
       <c r="D133" s="52"/>
       <c r="E133" s="53"/>
-      <c r="F133" s="32">
-        <v>27.9</v>
+      <c r="F133" s="6">
+        <v>43.9</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" s="25">
-        <v>307</v>
+        <v>22168</v>
       </c>
       <c r="B134" s="51"/>
       <c r="C134" s="52"/>
       <c r="D134" s="52"/>
       <c r="E134" s="53"/>
-      <c r="F134" s="32">
-        <v>36.9</v>
+      <c r="F134" s="6">
+        <v>53.9</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A135" s="25" t="s">
-        <v>168</v>
+      <c r="A135" s="25">
+        <v>22169</v>
       </c>
       <c r="B135" s="51"/>
       <c r="C135" s="52"/>
       <c r="D135" s="52"/>
       <c r="E135" s="53"/>
-      <c r="F135" s="32">
-        <v>39.9</v>
+      <c r="F135" s="6">
+        <v>43.9</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" s="25">
-        <v>308</v>
+        <v>22171</v>
       </c>
       <c r="B136" s="51"/>
       <c r="C136" s="52"/>
       <c r="D136" s="52"/>
       <c r="E136" s="53"/>
-      <c r="F136" s="32">
-        <v>32.9</v>
+      <c r="F136" s="6">
+        <v>54.9</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A137" s="25">
-        <v>309</v>
+      <c r="A137" s="25" t="inlineStr">
+        <is>
+          <t>22171E</t>
+        </is>
       </c>
       <c r="B137" s="51"/>
       <c r="C137" s="52"/>
       <c r="D137" s="52"/>
       <c r="E137" s="53"/>
-      <c r="F137" s="32">
-        <v>27.9</v>
+      <c r="F137" s="6">
+        <v>60</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" s="25">
-        <v>310</v>
+        <v>22172</v>
       </c>
       <c r="B138" s="51"/>
       <c r="C138" s="52"/>
       <c r="D138" s="52"/>
       <c r="E138" s="53"/>
-      <c r="F138" s="32">
-        <v>32.9</v>
+      <c r="F138" s="6">
+        <v>60.9</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A139" s="25" t="s">
-        <v>90</v>
+      <c r="A139" s="25" t="inlineStr">
+        <is>
+          <t>22172E</t>
+        </is>
       </c>
       <c r="B139" s="51"/>
       <c r="C139" s="52"/>
       <c r="D139" s="52"/>
       <c r="E139" s="53"/>
-      <c r="F139" s="32">
-        <v>36.9</v>
+      <c r="F139" s="6">
+        <v>63.9</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A140" s="26">
-        <v>316</v>
+      <c r="A140" s="25">
+        <v>22173</v>
       </c>
       <c r="B140" s="51"/>
       <c r="C140" s="52"/>
       <c r="D140" s="52"/>
       <c r="E140" s="53"/>
-      <c r="F140" s="32">
-        <v>32.9</v>
+      <c r="F140" s="6">
+        <v>68.9</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A141" s="26" t="s">
-        <v>91</v>
+      <c r="A141" s="25" t="inlineStr">
+        <is>
+          <t>22173E</t>
+        </is>
       </c>
       <c r="B141" s="51"/>
       <c r="C141" s="52"/>
       <c r="D141" s="52"/>
       <c r="E141" s="53"/>
-      <c r="F141" s="32">
-        <v>35.9</v>
+      <c r="F141" s="6">
+        <v>75.9</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A142" s="26">
-        <v>321</v>
+      <c r="A142" s="25">
+        <v>22174</v>
       </c>
       <c r="B142" s="51"/>
       <c r="C142" s="52"/>
       <c r="D142" s="52"/>
       <c r="E142" s="53"/>
       <c r="F142" s="6">
-        <v>39.9</v>
+        <v>72.9</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A143" s="25" t="s">
-        <v>93</v>
+      <c r="A143" s="25">
+        <v>22175</v>
       </c>
       <c r="B143" s="51"/>
       <c r="C143" s="52"/>
       <c r="D143" s="52"/>
       <c r="E143" s="53"/>
-      <c r="F143" s="32">
-        <v>41.9</v>
+      <c r="F143" s="6">
+        <v>72.9</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" s="25">
-        <v>325</v>
+        <v>22179</v>
       </c>
       <c r="B144" s="51"/>
       <c r="C144" s="52"/>
       <c r="D144" s="52"/>
       <c r="E144" s="53"/>
-      <c r="F144" s="32">
-        <v>39.9</v>
+      <c r="F144" s="6">
+        <v>32.9</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A145" s="25" t="s">
-        <v>94</v>
+      <c r="A145" s="25">
+        <v>22180</v>
       </c>
       <c r="B145" s="51"/>
       <c r="C145" s="52"/>
       <c r="D145" s="52"/>
       <c r="E145" s="53"/>
-      <c r="F145" s="32">
-        <v>41.9</v>
+      <c r="F145" s="6">
+        <v>65.9</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A146" s="25">
-        <v>327</v>
+        <v>22181</v>
       </c>
       <c r="B146" s="51"/>
       <c r="C146" s="52"/>
       <c r="D146" s="52"/>
       <c r="E146" s="53"/>
-      <c r="F146" s="32">
+      <c r="F146" s="6">
         <v>43.9</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A147" s="26" t="s">
-        <v>95</v>
+      <c r="A147" s="25">
+        <v>22182</v>
       </c>
       <c r="B147" s="51"/>
       <c r="C147" s="52"/>
       <c r="D147" s="52"/>
       <c r="E147" s="53"/>
-      <c r="F147" s="32">
-        <v>47.9</v>
+      <c r="F147" s="6">
+        <v>60.9</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A148" s="26">
-        <v>328</v>
+      <c r="A148" s="25">
+        <v>22183</v>
       </c>
       <c r="B148" s="51"/>
       <c r="C148" s="52"/>
       <c r="D148" s="52"/>
       <c r="E148" s="53"/>
-      <c r="F148" s="32">
-        <v>47.9</v>
+      <c r="F148" s="6">
+        <v>32.9</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A149" s="26" t="s">
-        <v>96</v>
+      <c r="A149" s="25">
+        <v>22184</v>
       </c>
       <c r="B149" s="51"/>
       <c r="C149" s="52"/>
       <c r="D149" s="52"/>
       <c r="E149" s="53"/>
-      <c r="F149" s="32">
-        <v>50.9</v>
+      <c r="F149" s="6">
+        <v>43.9</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A150" s="26">
-        <v>329</v>
+      <c r="A150" s="25">
+        <v>22185</v>
       </c>
       <c r="B150" s="51"/>
       <c r="C150" s="52"/>
       <c r="D150" s="52"/>
       <c r="E150" s="53"/>
-      <c r="F150" s="32">
-        <v>48.9</v>
+      <c r="F150" s="6">
+        <v>60.9</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A151" s="26" t="s">
-        <v>97</v>
+      <c r="A151" s="25">
+        <v>22186</v>
       </c>
       <c r="B151" s="51"/>
       <c r="C151" s="52"/>
       <c r="D151" s="52"/>
       <c r="E151" s="53"/>
-      <c r="F151" s="32">
-        <v>53.9</v>
+      <c r="F151" s="6">
+        <v>43.9</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A152" s="26">
-        <v>330</v>
+      <c r="A152" s="25">
+        <v>22187</v>
       </c>
       <c r="B152" s="51"/>
       <c r="C152" s="52"/>
       <c r="D152" s="52"/>
       <c r="E152" s="53"/>
-      <c r="F152" s="32">
-        <v>53.9</v>
+      <c r="F152" s="6">
+        <v>76.9</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A153" s="26" t="s">
-        <v>98</v>
+      <c r="A153" s="25">
+        <v>22188</v>
       </c>
       <c r="B153" s="51"/>
       <c r="C153" s="52"/>
       <c r="D153" s="52"/>
       <c r="E153" s="53"/>
-      <c r="F153" s="12">
-        <v>58.9</v>
+      <c r="F153" s="6">
+        <v>60.9</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A154" s="26">
-        <v>350</v>
+      <c r="A154" s="25">
+        <v>22189</v>
       </c>
       <c r="B154" s="51"/>
       <c r="C154" s="52"/>
       <c r="D154" s="52"/>
       <c r="E154" s="53"/>
       <c r="F154" s="6">
-        <v>44.9</v>
+        <v>72.9</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A155" s="25" t="s">
-        <v>99</v>
+      <c r="A155" s="25" t="inlineStr">
+        <is>
+          <t>22189E</t>
+        </is>
       </c>
       <c r="B155" s="51"/>
       <c r="C155" s="52"/>
       <c r="D155" s="52"/>
       <c r="E155" s="53"/>
       <c r="F155" s="6">
-        <v>49.9</v>
+        <v>79.9</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A156" s="25">
-        <v>352</v>
+        <v>22190</v>
       </c>
       <c r="B156" s="51"/>
       <c r="C156" s="52"/>
       <c r="D156" s="52"/>
       <c r="E156" s="53"/>
       <c r="F156" s="6">
-        <v>47.9</v>
+        <v>68.9</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A157" s="25">
-        <v>354</v>
+        <v>22191</v>
       </c>
       <c r="B157" s="51"/>
       <c r="C157" s="52"/>
       <c r="D157" s="52"/>
       <c r="E157" s="53"/>
       <c r="F157" s="6">
-        <v>42.9</v>
+        <v>65.9</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A158" s="25" t="s">
-        <v>169</v>
+      <c r="A158" s="25">
+        <v>22192</v>
       </c>
       <c r="B158" s="51"/>
       <c r="C158" s="52"/>
       <c r="D158" s="52"/>
       <c r="E158" s="53"/>
       <c r="F158" s="6">
-        <v>45.9</v>
+        <v>65.9</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A159" s="25">
-        <v>355</v>
+        <v>22194</v>
       </c>
       <c r="B159" s="51"/>
       <c r="C159" s="52"/>
       <c r="D159" s="52"/>
       <c r="E159" s="53"/>
       <c r="F159" s="6">
-        <v>41.9</v>
+        <v>72.9</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A160" s="25" t="s">
-        <v>170</v>
+      <c r="A160" s="25">
+        <v>22195</v>
       </c>
       <c r="B160" s="51"/>
       <c r="C160" s="52"/>
       <c r="D160" s="52"/>
       <c r="E160" s="53"/>
       <c r="F160" s="6">
-        <v>46.9</v>
+        <v>80.9</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161" s="25">
-        <v>358</v>
+        <v>22196</v>
       </c>
       <c r="B161" s="51"/>
       <c r="C161" s="52"/>
       <c r="D161" s="52"/>
       <c r="E161" s="53"/>
       <c r="F161" s="6">
-        <v>37.9</v>
+        <v>76.9</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A162" s="25" t="s">
-        <v>171</v>
+      <c r="A162" s="25">
+        <v>22197</v>
       </c>
       <c r="B162" s="51"/>
       <c r="C162" s="52"/>
       <c r="D162" s="52"/>
       <c r="E162" s="53"/>
       <c r="F162" s="6">
-        <v>40.9</v>
+        <v>65.9</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163" s="25">
-        <v>359</v>
+        <v>22198</v>
       </c>
       <c r="B163" s="51"/>
       <c r="C163" s="52"/>
       <c r="D163" s="52"/>
       <c r="E163" s="53"/>
       <c r="F163" s="6">
-        <v>37.9</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A164" s="25" t="s">
-        <v>191</v>
+      <c r="A164" s="25">
+        <v>22199</v>
       </c>
       <c r="B164" s="51"/>
       <c r="C164" s="52"/>
       <c r="D164" s="52"/>
       <c r="E164" s="53"/>
       <c r="F164" s="6">
-        <v>40.9</v>
+        <v>66.9</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A165" s="26">
-        <v>380</v>
+      <c r="A165" s="25" t="inlineStr">
+        <is>
+          <t>22199E</t>
+        </is>
       </c>
       <c r="B165" s="51"/>
       <c r="C165" s="52"/>
       <c r="D165" s="52"/>
       <c r="E165" s="53"/>
       <c r="F165" s="6">
-        <v>29.9</v>
+        <v>73.9</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A166" s="26" t="s">
-        <v>101</v>
+      <c r="A166" s="25">
+        <v>22200</v>
       </c>
       <c r="B166" s="51"/>
       <c r="C166" s="52"/>
       <c r="D166" s="52"/>
       <c r="E166" s="53"/>
       <c r="F166" s="6">
-        <v>32.9</v>
+        <v>65.9</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A167" s="26">
-        <v>390</v>
+      <c r="A167" s="25">
+        <v>22201</v>
       </c>
       <c r="B167" s="51"/>
       <c r="C167" s="52"/>
       <c r="D167" s="52"/>
       <c r="E167" s="53"/>
-      <c r="F167" s="32">
-        <v>36.9</v>
+      <c r="F167" s="6">
+        <v>65.9</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A168" s="26" t="s">
-        <v>102</v>
+      <c r="A168" s="25">
+        <v>22202</v>
       </c>
       <c r="B168" s="51"/>
       <c r="C168" s="52"/>
       <c r="D168" s="52"/>
       <c r="E168" s="53"/>
-      <c r="F168" s="32">
-        <v>39.9</v>
+      <c r="F168" s="6">
+        <v>69.9</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A169" s="25">
-        <v>402</v>
+        <v>22205</v>
       </c>
       <c r="B169" s="51"/>
       <c r="C169" s="52"/>
       <c r="D169" s="52"/>
       <c r="E169" s="53"/>
       <c r="F169" s="6">
-        <v>49.9</v>
+        <v>87.9</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A170" s="25" t="s">
-        <v>192</v>
+      <c r="A170" s="25">
+        <v>22212</v>
       </c>
       <c r="B170" s="51"/>
       <c r="C170" s="52"/>
       <c r="D170" s="52"/>
       <c r="E170" s="53"/>
-      <c r="F170" s="12">
-        <v>52.9</v>
+      <c r="F170" s="6">
+        <v>74.9</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A171" s="26">
-        <v>403</v>
+      <c r="A171" s="25">
+        <v>22213</v>
       </c>
       <c r="B171" s="51"/>
       <c r="C171" s="52"/>
       <c r="D171" s="52"/>
       <c r="E171" s="53"/>
       <c r="F171" s="6">
-        <v>45</v>
+        <v>131.9</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A172" s="25">
-        <v>404</v>
+        <v>22214</v>
       </c>
       <c r="B172" s="51"/>
       <c r="C172" s="52"/>
       <c r="D172" s="52"/>
       <c r="E172" s="53"/>
-      <c r="F172" s="32">
-        <v>36.9</v>
+      <c r="F172" s="6">
+        <v>142.9</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A173" s="25">
-        <v>407</v>
+        <v>22215</v>
       </c>
       <c r="B173" s="51"/>
       <c r="C173" s="52"/>
       <c r="D173" s="52"/>
       <c r="E173" s="53"/>
-      <c r="F173" s="32">
-        <v>29.9</v>
+      <c r="F173" s="6">
+        <v>87.9</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A174" s="25">
-        <v>429</v>
+        <v>22216</v>
       </c>
       <c r="B174" s="51"/>
       <c r="C174" s="52"/>
       <c r="D174" s="52"/>
       <c r="E174" s="53"/>
-      <c r="F174" s="12">
-        <v>52.9</v>
+      <c r="F174" s="6">
+        <v>87.9</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A175" s="25" t="s">
-        <v>106</v>
+      <c r="A175" s="25">
+        <v>22217</v>
       </c>
       <c r="B175" s="51"/>
       <c r="C175" s="52"/>
       <c r="D175" s="52"/>
       <c r="E175" s="53"/>
       <c r="F175" s="6">
-        <v>57.9</v>
+        <v>87.9</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176" s="25">
-        <v>430</v>
+        <v>22218</v>
       </c>
       <c r="B176" s="51"/>
       <c r="C176" s="52"/>
       <c r="D176" s="52"/>
       <c r="E176" s="53"/>
-      <c r="F176" s="32">
-        <v>54.9</v>
+      <c r="F176" s="6">
+        <v>87.9</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A177" s="25" t="s">
-        <v>107</v>
+      <c r="A177" s="25">
+        <v>22219</v>
       </c>
       <c r="B177" s="51"/>
       <c r="C177" s="52"/>
       <c r="D177" s="52"/>
       <c r="E177" s="53"/>
       <c r="F177" s="6">
-        <v>60.9</v>
+        <v>98.9</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A178" s="25">
-        <v>499</v>
+        <v>22230</v>
       </c>
       <c r="B178" s="51"/>
       <c r="C178" s="52"/>
       <c r="D178" s="52"/>
       <c r="E178" s="53"/>
-      <c r="F178" s="32">
-        <v>41.9</v>
+      <c r="F178" s="6">
+        <v>91.9</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A179" s="25" t="s">
-        <v>109</v>
+      <c r="A179" s="25">
+        <v>22231</v>
       </c>
       <c r="B179" s="51"/>
       <c r="C179" s="52"/>
       <c r="D179" s="52"/>
       <c r="E179" s="53"/>
-      <c r="F179" s="12">
-        <v>44.9</v>
+      <c r="F179" s="6">
+        <v>94.9</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A180" s="25">
-        <v>500</v>
+        <v>22233</v>
       </c>
       <c r="B180" s="51"/>
       <c r="C180" s="52"/>
       <c r="D180" s="52"/>
       <c r="E180" s="53"/>
       <c r="F180" s="6">
-        <v>26.9</v>
+        <v>98.9</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A181" s="26" t="s">
-        <v>110</v>
+      <c r="A181" s="25">
+        <v>22235</v>
       </c>
       <c r="B181" s="51"/>
       <c r="C181" s="52"/>
       <c r="D181" s="52"/>
       <c r="E181" s="53"/>
-      <c r="F181" s="12">
-        <v>29.9</v>
+      <c r="F181" s="6">
+        <v>92.9</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A182" s="25">
-        <v>501</v>
+        <v>22236</v>
       </c>
       <c r="B182" s="51"/>
       <c r="C182" s="52"/>
       <c r="D182" s="52"/>
       <c r="E182" s="53"/>
-      <c r="F182" s="12">
-        <v>35.9</v>
+      <c r="F182" s="6">
+        <v>54.9</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A183" s="25" t="s">
-        <v>172</v>
+      <c r="A183" s="25">
+        <v>22237</v>
       </c>
       <c r="B183" s="51"/>
       <c r="C183" s="52"/>
       <c r="D183" s="52"/>
       <c r="E183" s="53"/>
       <c r="F183" s="6">
-        <v>37.9</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A184" s="25">
-        <v>502</v>
+        <v>22238</v>
       </c>
       <c r="B184" s="51"/>
       <c r="C184" s="52"/>
       <c r="D184" s="52"/>
       <c r="E184" s="53"/>
       <c r="F184" s="6">
-        <v>30.9</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A185" s="25" t="s">
-        <v>111</v>
+      <c r="A185" s="25">
+        <v>22239</v>
       </c>
       <c r="B185" s="51"/>
       <c r="C185" s="52"/>
       <c r="D185" s="52"/>
       <c r="E185" s="53"/>
       <c r="F185" s="6">
-        <v>32.9</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A186" s="25">
-        <v>550</v>
+        <v>22240</v>
       </c>
       <c r="B186" s="51"/>
       <c r="C186" s="52"/>
       <c r="D186" s="52"/>
       <c r="E186" s="53"/>
       <c r="F186" s="6">
-        <v>17.899999999999999</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A187" s="25" t="s">
-        <v>112</v>
+      <c r="A187" s="25">
+        <v>22242</v>
       </c>
       <c r="B187" s="51"/>
       <c r="C187" s="52"/>
       <c r="D187" s="52"/>
       <c r="E187" s="53"/>
       <c r="F187" s="6">
-        <v>19.899999999999999</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A188" s="26">
-        <v>570</v>
+      <c r="A188" s="25">
+        <v>22243</v>
       </c>
       <c r="B188" s="51"/>
       <c r="C188" s="52"/>
       <c r="D188" s="52"/>
       <c r="E188" s="53"/>
       <c r="F188" s="6">
-        <v>48.9</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A189" s="26" t="s">
-        <v>113</v>
+      <c r="A189" s="25">
+        <v>22244</v>
       </c>
       <c r="B189" s="51"/>
       <c r="C189" s="52"/>
       <c r="D189" s="52"/>
       <c r="E189" s="53"/>
       <c r="F189" s="6">
-        <v>52.9</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A190" s="25">
-        <v>582</v>
+        <v>22246</v>
       </c>
       <c r="B190" s="51"/>
       <c r="C190" s="52"/>
       <c r="D190" s="52"/>
       <c r="E190" s="53"/>
       <c r="F190" s="6">
-        <v>43.9</v>
+        <v>87.9</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A191" s="25" t="s">
-        <v>116</v>
+      <c r="A191" s="25">
+        <v>22471</v>
       </c>
       <c r="B191" s="51"/>
       <c r="C191" s="52"/>
       <c r="D191" s="52"/>
       <c r="E191" s="53"/>
-      <c r="F191" s="12">
-        <v>48.9</v>
+      <c r="F191" s="6">
+        <v>50.9</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A192" s="26">
-        <v>590</v>
+      <c r="A192" s="25">
+        <v>22511</v>
       </c>
       <c r="B192" s="51"/>
       <c r="C192" s="52"/>
       <c r="D192" s="52"/>
       <c r="E192" s="53"/>
       <c r="F192" s="6">
-        <v>42.9</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A193" s="25" t="s">
-        <v>117</v>
+      <c r="A193" s="25">
+        <v>22521</v>
       </c>
       <c r="B193" s="51"/>
       <c r="C193" s="52"/>
       <c r="D193" s="52"/>
       <c r="E193" s="53"/>
-      <c r="F193" s="32">
-        <v>45.9</v>
+      <c r="F193" s="6">
+        <v>42.9</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A194" s="26">
-        <v>595</v>
+      <c r="A194" s="25">
+        <v>22531</v>
       </c>
       <c r="B194" s="51"/>
       <c r="C194" s="52"/>
       <c r="D194" s="52"/>
       <c r="E194" s="53"/>
       <c r="F194" s="6">
-        <v>76.900000000000006</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A195" s="25" t="s">
-        <v>118</v>
+      <c r="A195" s="25">
+        <v>22561</v>
       </c>
       <c r="B195" s="51"/>
       <c r="C195" s="52"/>
       <c r="D195" s="52"/>
       <c r="E195" s="53"/>
-      <c r="F195" s="32">
-        <v>83.9</v>
+      <c r="F195" s="6">
+        <v>51.9</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A196" s="25">
-        <v>601</v>
+        <v>22571</v>
       </c>
       <c r="B196" s="51"/>
       <c r="C196" s="52"/>
       <c r="D196" s="52"/>
       <c r="E196" s="53"/>
       <c r="F196" s="6">
-        <v>32.9</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A197" s="25" t="s">
-        <v>120</v>
+      <c r="A197" s="25">
+        <v>22581</v>
       </c>
       <c r="B197" s="51"/>
       <c r="C197" s="52"/>
       <c r="D197" s="52"/>
       <c r="E197" s="53"/>
       <c r="F197" s="6">
-        <v>36.9</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A198" s="25">
-        <v>605</v>
+        <v>22601</v>
       </c>
       <c r="B198" s="51"/>
       <c r="C198" s="52"/>
       <c r="D198" s="52"/>
       <c r="E198" s="53"/>
       <c r="F198" s="6">
-        <v>29.9</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A199" s="25" t="s">
-        <v>121</v>
+      <c r="A199" s="25">
+        <v>22821</v>
       </c>
       <c r="B199" s="51"/>
       <c r="C199" s="52"/>
       <c r="D199" s="52"/>
       <c r="E199" s="53"/>
-      <c r="F199" s="12">
-        <v>31.9</v>
+      <c r="F199" s="6">
+        <v>76.9</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A200" s="25">
-        <v>640</v>
+        <v>22831</v>
       </c>
       <c r="B200" s="51"/>
       <c r="C200" s="52"/>
       <c r="D200" s="52"/>
       <c r="E200" s="53"/>
       <c r="F200" s="6">
-        <v>42.9</v>
+        <v>76.9</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A201" s="25" t="s">
-        <v>122</v>
+      <c r="A201" s="25">
+        <v>221111</v>
       </c>
       <c r="B201" s="51"/>
       <c r="C201" s="52"/>
       <c r="D201" s="52"/>
       <c r="E201" s="53"/>
       <c r="F201" s="6">
-        <v>45.9</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A202" s="25">
-        <v>650</v>
-      </c>
       <c r="B202" s="51"/>
       <c r="C202" s="52"/>
       <c r="D202" s="52"/>
       <c r="E202" s="53"/>
-      <c r="F202" s="6">
-        <v>39.9</v>
-      </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A203" s="25" t="s">
-        <v>123</v>
-      </c>
       <c r="B203" s="51"/>
       <c r="C203" s="52"/>
       <c r="D203" s="52"/>
       <c r="E203" s="53"/>
-      <c r="F203" s="6">
-        <v>43.9</v>
-      </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A204" s="25">
-        <v>690</v>
-      </c>
       <c r="B204" s="51"/>
       <c r="C204" s="52"/>
       <c r="D204" s="52"/>
       <c r="E204" s="53"/>
-      <c r="F204" s="6">
-        <v>42.9</v>
-      </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A205" s="25" t="s">
-        <v>124</v>
-      </c>
       <c r="B205" s="51"/>
       <c r="C205" s="52"/>
       <c r="D205" s="52"/>
       <c r="E205" s="53"/>
-      <c r="F205" s="12">
-        <v>46.9</v>
-      </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A206" s="25">
-        <v>702</v>
-      </c>
       <c r="B206" s="51"/>
       <c r="C206" s="52"/>
       <c r="D206" s="52"/>
       <c r="E206" s="53"/>
-      <c r="F206" s="6">
-        <v>29.9</v>
-      </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A207" s="25" t="s">
-        <v>173</v>
-      </c>
       <c r="B207" s="51"/>
       <c r="C207" s="52"/>
       <c r="D207" s="52"/>
       <c r="E207" s="53"/>
-      <c r="F207" s="6">
-        <v>32.9</v>
-      </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A208" s="25">
-        <v>703</v>
-      </c>
       <c r="B208" s="51"/>
       <c r="C208" s="52"/>
       <c r="D208" s="52"/>
       <c r="E208" s="53"/>
-      <c r="F208" s="6">
-        <v>31.9</v>
-      </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A209" s="25" t="s">
-        <v>174</v>
-      </c>
       <c r="B209" s="51"/>
       <c r="C209" s="52"/>
       <c r="D209" s="52"/>
       <c r="E209" s="53"/>
-      <c r="F209" s="6">
-        <v>42.9</v>
-      </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A210" s="25">
-        <v>704</v>
-      </c>
       <c r="B210" s="51"/>
       <c r="C210" s="52"/>
       <c r="D210" s="52"/>
       <c r="E210" s="53"/>
-      <c r="F210" s="6">
-        <v>36.9</v>
-      </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A211" s="25" t="s">
-        <v>175</v>
-      </c>
       <c r="B211" s="51"/>
       <c r="C211" s="52"/>
       <c r="D211" s="52"/>
       <c r="E211" s="53"/>
-      <c r="F211" s="6">
-        <v>39.9</v>
-      </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A212" s="25">
-        <v>705</v>
-      </c>
       <c r="B212" s="51"/>
       <c r="C212" s="52"/>
       <c r="D212" s="52"/>
       <c r="E212" s="53"/>
-      <c r="F212" s="6">
-        <v>38.9</v>
-      </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A213" s="25" t="s">
-        <v>176</v>
-      </c>
       <c r="B213" s="51"/>
       <c r="C213" s="52"/>
       <c r="D213" s="52"/>
       <c r="E213" s="53"/>
-      <c r="F213" s="6">
-        <v>49.9</v>
-      </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A214" s="25">
-        <v>706</v>
-      </c>
       <c r="B214" s="51"/>
       <c r="C214" s="52"/>
       <c r="D214" s="52"/>
       <c r="E214" s="53"/>
-      <c r="F214" s="6">
-        <v>41.9</v>
-      </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A215" s="25" t="s">
-        <v>177</v>
-      </c>
       <c r="B215" s="51"/>
       <c r="C215" s="52"/>
       <c r="D215" s="52"/>
       <c r="E215" s="53"/>
-      <c r="F215" s="6">
-        <v>52.9</v>
-      </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A216" s="25">
-        <v>707</v>
-      </c>
       <c r="B216" s="51"/>
       <c r="C216" s="52"/>
       <c r="D216" s="52"/>
       <c r="E216" s="53"/>
-      <c r="F216" s="6">
-        <v>30.9</v>
-      </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A217" s="25">
-        <v>710</v>
-      </c>
       <c r="B217" s="51"/>
       <c r="C217" s="52"/>
       <c r="D217" s="52"/>
       <c r="E217" s="53"/>
-      <c r="F217" s="12">
-        <v>30.9</v>
-      </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A218" s="25" t="s">
-        <v>125</v>
-      </c>
       <c r="B218" s="51"/>
       <c r="C218" s="52"/>
       <c r="D218" s="52"/>
       <c r="E218" s="53"/>
-      <c r="F218" s="32">
-        <v>32.9</v>
-      </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A219" s="25">
-        <v>714</v>
-      </c>
       <c r="B219" s="51"/>
       <c r="C219" s="52"/>
       <c r="D219" s="52"/>
       <c r="E219" s="53"/>
-      <c r="F219" s="12">
-        <v>44.9</v>
-      </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A220" s="25" t="s">
-        <v>178</v>
-      </c>
       <c r="B220" s="51"/>
       <c r="C220" s="52"/>
       <c r="D220" s="52"/>
       <c r="E220" s="53"/>
-      <c r="F220" s="12">
-        <v>48.9</v>
-      </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A221" s="25">
-        <v>715</v>
-      </c>
       <c r="B221" s="51"/>
       <c r="C221" s="52"/>
       <c r="D221" s="52"/>
       <c r="E221" s="53"/>
-      <c r="F221" s="12">
-        <v>41.9</v>
-      </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A222" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="B222" s="51"/>
       <c r="C222" s="52"/>
       <c r="D222" s="52"/>
       <c r="E222" s="53"/>
-      <c r="F222" s="12">
-        <v>46.9</v>
-      </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A223" s="25">
-        <v>716</v>
-      </c>
       <c r="B223" s="51"/>
       <c r="C223" s="52"/>
       <c r="D223" s="52"/>
       <c r="E223" s="53"/>
-      <c r="F223" s="12">
-        <v>54.9</v>
-      </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A224" s="25" t="s">
-        <v>180</v>
-      </c>
       <c r="B224" s="51"/>
       <c r="C224" s="52"/>
       <c r="D224" s="52"/>
       <c r="E224" s="53"/>
-      <c r="F224" s="12">
-        <v>60.9</v>
-      </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A225" s="25">
-        <v>719</v>
-      </c>
       <c r="B225" s="51"/>
       <c r="C225" s="52"/>
       <c r="D225" s="52"/>
       <c r="E225" s="53"/>
-      <c r="F225" s="12">
-        <v>42.9</v>
-      </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A226" s="25" t="s">
-        <v>193</v>
-      </c>
       <c r="B226" s="51"/>
       <c r="C226" s="52"/>
       <c r="D226" s="52"/>
       <c r="E226" s="53"/>
-      <c r="F226" s="12">
-        <v>45.9</v>
-      </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A227" s="25">
-        <v>720</v>
-      </c>
       <c r="B227" s="51"/>
       <c r="C227" s="52"/>
       <c r="D227" s="52"/>
       <c r="E227" s="53"/>
-      <c r="F227" s="12">
-        <v>36.9</v>
-      </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A228" s="26" t="s">
-        <v>127</v>
-      </c>
       <c r="B228" s="51"/>
       <c r="C228" s="52"/>
       <c r="D228" s="52"/>
       <c r="E228" s="53"/>
-      <c r="F228" s="12">
-        <v>39.9</v>
-      </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A229" s="25">
-        <v>730</v>
-      </c>
       <c r="B229" s="51"/>
       <c r="C229" s="52"/>
       <c r="D229" s="52"/>
       <c r="E229" s="53"/>
-      <c r="F229" s="6">
-        <v>39.9</v>
-      </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A230" s="25" t="s">
-        <v>129</v>
-      </c>
       <c r="B230" s="51"/>
       <c r="C230" s="52"/>
       <c r="D230" s="52"/>
       <c r="E230" s="53"/>
-      <c r="F230" s="6">
-        <v>42.9</v>
-      </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A231" s="25">
-        <v>750</v>
-      </c>
       <c r="B231" s="51"/>
       <c r="C231" s="52"/>
       <c r="D231" s="52"/>
       <c r="E231" s="53"/>
-      <c r="F231" s="6">
-        <v>36.9</v>
-      </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A232" s="26" t="s">
-        <v>130</v>
-      </c>
       <c r="B232" s="51"/>
       <c r="C232" s="52"/>
       <c r="D232" s="52"/>
       <c r="E232" s="53"/>
-      <c r="F232" s="6">
-        <v>39.9</v>
-      </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A233" s="25">
-        <v>760</v>
-      </c>
       <c r="B233" s="51"/>
       <c r="C233" s="52"/>
       <c r="D233" s="52"/>
       <c r="E233" s="53"/>
-      <c r="F233" s="6">
-        <v>39.9</v>
-      </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A234" s="25" t="s">
-        <v>131</v>
-      </c>
       <c r="B234" s="51"/>
       <c r="C234" s="52"/>
       <c r="D234" s="52"/>
       <c r="E234" s="53"/>
-      <c r="F234" s="6">
-        <v>43.9</v>
-      </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A235" s="25">
-        <v>770</v>
-      </c>
       <c r="B235" s="51"/>
       <c r="C235" s="52"/>
       <c r="D235" s="52"/>
       <c r="E235" s="53"/>
-      <c r="F235" s="6">
-        <v>32.9</v>
-      </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A236" s="25" t="s">
-        <v>132</v>
-      </c>
       <c r="B236" s="51"/>
       <c r="C236" s="52"/>
       <c r="D236" s="52"/>
       <c r="E236" s="53"/>
-      <c r="F236" s="6">
-        <v>36.9</v>
-      </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A237" s="25">
-        <v>800</v>
-      </c>
       <c r="B237" s="51"/>
       <c r="C237" s="52"/>
       <c r="D237" s="52"/>
       <c r="E237" s="53"/>
-      <c r="F237" s="6">
-        <v>40.9</v>
-      </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A238" s="25" t="s">
-        <v>133</v>
-      </c>
       <c r="B238" s="51"/>
       <c r="C238" s="52"/>
       <c r="D238" s="52"/>
       <c r="E238" s="53"/>
-      <c r="F238" s="6">
-        <v>43.9</v>
-      </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A239" s="27">
-        <v>810</v>
-      </c>
       <c r="B239" s="51"/>
       <c r="C239" s="52"/>
       <c r="D239" s="52"/>
       <c r="E239" s="53"/>
-      <c r="F239" s="6">
-        <v>18.899999999999999</v>
-      </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A240" s="25">
-        <v>815</v>
-      </c>
       <c r="B240" s="51"/>
       <c r="C240" s="52"/>
       <c r="D240" s="52"/>
       <c r="E240" s="53"/>
-      <c r="F240" s="6">
-        <v>36.9</v>
-      </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A241" s="25">
-        <v>816</v>
-      </c>
       <c r="B241" s="51"/>
       <c r="C241" s="52"/>
       <c r="D241" s="52"/>
       <c r="E241" s="53"/>
-      <c r="F241" s="6">
-        <v>36.9</v>
-      </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A242" s="29">
-        <v>819</v>
-      </c>
       <c r="B242" s="51"/>
       <c r="C242" s="52"/>
       <c r="D242" s="52"/>
       <c r="E242" s="53"/>
-      <c r="F242" s="6">
-        <v>37.9</v>
-      </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A243" s="30">
-        <v>841</v>
-      </c>
       <c r="B243" s="51"/>
       <c r="C243" s="52"/>
       <c r="D243" s="52"/>
       <c r="E243" s="53"/>
-      <c r="F243" s="7">
-        <v>39.9</v>
-      </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A244" s="30" t="s">
-        <v>135</v>
-      </c>
       <c r="B244" s="51"/>
       <c r="C244" s="52"/>
       <c r="D244" s="52"/>
       <c r="E244" s="53"/>
-      <c r="F244" s="7">
-        <v>43.9</v>
-      </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A245" s="30">
-        <v>845</v>
-      </c>
       <c r="B245" s="51"/>
       <c r="C245" s="52"/>
       <c r="D245" s="52"/>
       <c r="E245" s="53"/>
-      <c r="F245" s="7">
-        <v>39.9</v>
-      </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A246" s="30" t="s">
-        <v>136</v>
-      </c>
       <c r="B246" s="51"/>
       <c r="C246" s="52"/>
       <c r="D246" s="52"/>
       <c r="E246" s="53"/>
-      <c r="F246" s="7">
-        <v>43.9</v>
-      </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A247" s="30">
-        <v>848</v>
-      </c>
       <c r="B247" s="51"/>
       <c r="C247" s="52"/>
       <c r="D247" s="52"/>
       <c r="E247" s="53"/>
-      <c r="F247" s="7">
-        <v>43.9</v>
-      </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A248" s="30" t="s">
-        <v>194</v>
-      </c>
       <c r="B248" s="51"/>
       <c r="C248" s="52"/>
       <c r="D248" s="52"/>
       <c r="E248" s="53"/>
-      <c r="F248" s="7">
-        <v>48.9</v>
-      </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A249" s="30">
-        <v>849</v>
-      </c>
       <c r="B249" s="51"/>
       <c r="C249" s="52"/>
       <c r="D249" s="52"/>
       <c r="E249" s="53"/>
-      <c r="F249" s="7">
-        <v>46.9</v>
-      </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A250" s="30" t="s">
-        <v>195</v>
-      </c>
       <c r="B250" s="51"/>
       <c r="C250" s="52"/>
       <c r="D250" s="52"/>
       <c r="E250" s="53"/>
-      <c r="F250" s="7">
-        <v>50.9</v>
-      </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A251" s="30">
-        <v>851</v>
-      </c>
       <c r="B251" s="51"/>
       <c r="C251" s="52"/>
       <c r="D251" s="52"/>
       <c r="E251" s="53"/>
-      <c r="F251" s="7">
-        <v>54.9</v>
-      </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A252" s="26" t="s">
-        <v>196</v>
-      </c>
       <c r="B252" s="51"/>
       <c r="C252" s="52"/>
       <c r="D252" s="52"/>
       <c r="E252" s="53"/>
-      <c r="F252" s="7">
-        <v>60</v>
-      </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A253" s="26">
-        <v>852</v>
-      </c>
       <c r="B253" s="51"/>
       <c r="C253" s="52"/>
       <c r="D253" s="52"/>
       <c r="E253" s="53"/>
-      <c r="F253" s="7">
-        <v>53.9</v>
-      </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A254" s="26" t="s">
-        <v>137</v>
-      </c>
       <c r="B254" s="51"/>
       <c r="C254" s="52"/>
       <c r="D254" s="52"/>
       <c r="E254" s="53"/>
-      <c r="F254" s="7">
-        <v>58.9</v>
-      </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A255" s="26">
-        <v>853</v>
-      </c>
       <c r="B255" s="51"/>
       <c r="C255" s="52"/>
       <c r="D255" s="52"/>
       <c r="E255" s="53"/>
-      <c r="F255" s="7">
-        <v>54.9</v>
-      </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A256" s="26" t="s">
-        <v>138</v>
-      </c>
       <c r="B256" s="51"/>
       <c r="C256" s="52"/>
       <c r="D256" s="52"/>
       <c r="E256" s="53"/>
-      <c r="F256" s="7">
-        <v>60</v>
-      </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A257" s="26">
-        <v>854</v>
-      </c>
       <c r="B257" s="51"/>
       <c r="C257" s="52"/>
       <c r="D257" s="52"/>
       <c r="E257" s="53"/>
-      <c r="F257" s="7">
-        <v>51.9</v>
-      </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A258" s="26" t="s">
-        <v>139</v>
-      </c>
       <c r="B258" s="51"/>
       <c r="C258" s="52"/>
       <c r="D258" s="52"/>
       <c r="E258" s="53"/>
-      <c r="F258" s="7">
-        <v>56</v>
-      </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A259" s="26">
-        <v>855</v>
-      </c>
       <c r="B259" s="51"/>
       <c r="C259" s="52"/>
       <c r="D259" s="52"/>
       <c r="E259" s="53"/>
-      <c r="F259" s="7">
-        <v>54.9</v>
-      </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A260" s="26" t="s">
-        <v>140</v>
-      </c>
       <c r="B260" s="51"/>
       <c r="C260" s="52"/>
       <c r="D260" s="52"/>
       <c r="E260" s="53"/>
-      <c r="F260" s="7">
-        <v>60.9</v>
-      </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A261" s="26">
-        <v>870</v>
-      </c>
       <c r="B261" s="51"/>
       <c r="C261" s="52"/>
       <c r="D261" s="52"/>
       <c r="E261" s="53"/>
-      <c r="F261" s="7">
-        <v>58.9</v>
-      </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A262" s="26" t="s">
-        <v>141</v>
-      </c>
       <c r="B262" s="51"/>
       <c r="C262" s="52"/>
       <c r="D262" s="52"/>
       <c r="E262" s="53"/>
-      <c r="F262" s="7">
-        <v>63.9</v>
-      </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A263" s="26">
-        <v>880</v>
-      </c>
       <c r="B263" s="51"/>
       <c r="C263" s="52"/>
       <c r="D263" s="52"/>
       <c r="E263" s="53"/>
-      <c r="F263" s="7">
-        <v>58.9</v>
-      </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A264" s="26" t="s">
-        <v>142</v>
-      </c>
       <c r="B264" s="51"/>
       <c r="C264" s="52"/>
       <c r="D264" s="52"/>
       <c r="E264" s="53"/>
-      <c r="F264" s="7">
-        <v>64.900000000000006</v>
-      </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A265" s="26">
-        <v>890</v>
-      </c>
       <c r="B265" s="51"/>
       <c r="C265" s="52"/>
       <c r="D265" s="52"/>
       <c r="E265" s="53"/>
-      <c r="F265" s="7">
-        <v>62.9</v>
-      </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A266" s="26">
-        <v>901</v>
-      </c>
       <c r="B266" s="51"/>
       <c r="C266" s="52"/>
       <c r="D266" s="52"/>
       <c r="E266" s="53"/>
-      <c r="F266" s="7">
-        <v>32.9</v>
-      </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A267" s="26" t="s">
-        <v>143</v>
-      </c>
       <c r="B267" s="51"/>
       <c r="C267" s="52"/>
       <c r="D267" s="52"/>
       <c r="E267" s="53"/>
-      <c r="F267" s="7">
-        <v>36.9</v>
-      </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A268" s="26">
-        <v>911</v>
-      </c>
       <c r="B268" s="51"/>
       <c r="C268" s="52"/>
       <c r="D268" s="52"/>
       <c r="E268" s="53"/>
-      <c r="F268" s="7">
-        <v>32.9</v>
-      </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A269" s="26" t="s">
-        <v>144</v>
-      </c>
       <c r="B269" s="51"/>
       <c r="C269" s="52"/>
       <c r="D269" s="52"/>
       <c r="E269" s="53"/>
-      <c r="F269" s="7">
-        <v>36.9</v>
-      </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A270" s="26">
-        <v>981</v>
-      </c>
       <c r="B270" s="51"/>
       <c r="C270" s="52"/>
       <c r="D270" s="52"/>
       <c r="E270" s="53"/>
-      <c r="F270" s="7">
-        <v>39.9</v>
-      </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A271" s="26">
-        <v>990</v>
-      </c>
       <c r="B271" s="51"/>
       <c r="C271" s="52"/>
       <c r="D271" s="52"/>
       <c r="E271" s="53"/>
-      <c r="F271" s="7">
-        <v>62.9</v>
-      </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A272" s="26" t="s">
-        <v>197</v>
-      </c>
       <c r="B272" s="51"/>
       <c r="C272" s="52"/>
       <c r="D272" s="52"/>
       <c r="E272" s="53"/>
-      <c r="F272" s="7">
-        <v>68.900000000000006</v>
-      </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A273" s="26">
-        <v>1001</v>
-      </c>
       <c r="B273" s="51"/>
       <c r="C273" s="52"/>
       <c r="D273" s="52"/>
       <c r="E273" s="53"/>
-      <c r="F273" s="7">
-        <v>76.900000000000006</v>
-      </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A274" s="26" t="s">
-        <v>198</v>
-      </c>
       <c r="B274" s="51"/>
       <c r="C274" s="52"/>
       <c r="D274" s="52"/>
       <c r="E274" s="53"/>
-      <c r="F274" s="7">
-        <v>83.9</v>
-      </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A275" s="26">
-        <v>1002</v>
-      </c>
       <c r="B275" s="51"/>
       <c r="C275" s="52"/>
       <c r="D275" s="52"/>
       <c r="E275" s="53"/>
-      <c r="F275" s="7">
-        <v>65.900000000000006</v>
-      </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A276" s="26" t="s">
-        <v>199</v>
-      </c>
       <c r="B276" s="51"/>
       <c r="C276" s="52"/>
       <c r="D276" s="52"/>
       <c r="E276" s="53"/>
-      <c r="F276" s="7">
-        <v>71.900000000000006</v>
-      </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A277" s="26">
-        <v>1003</v>
-      </c>
       <c r="B277" s="51"/>
       <c r="C277" s="52"/>
       <c r="D277" s="52"/>
       <c r="E277" s="53"/>
-      <c r="F277" s="7">
-        <v>71.900000000000006</v>
-      </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A278" s="26" t="s">
-        <v>200</v>
-      </c>
       <c r="B278" s="51"/>
       <c r="C278" s="52"/>
       <c r="D278" s="52"/>
       <c r="E278" s="53"/>
-      <c r="F278" s="7">
-        <v>76.900000000000006</v>
-      </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A279" s="26">
-        <v>1004</v>
-      </c>
       <c r="B279" s="51"/>
       <c r="C279" s="52"/>
       <c r="D279" s="52"/>
       <c r="E279" s="53"/>
-      <c r="F279" s="7">
-        <v>87.9</v>
-      </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A280" s="26" t="s">
-        <v>201</v>
-      </c>
       <c r="B280" s="51"/>
       <c r="C280" s="52"/>
       <c r="D280" s="52"/>
       <c r="E280" s="53"/>
-      <c r="F280" s="7">
-        <v>95.9</v>
-      </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A281" s="26">
-        <v>1005</v>
-      </c>
       <c r="B281" s="51"/>
       <c r="C281" s="52"/>
       <c r="D281" s="52"/>
       <c r="E281" s="53"/>
-      <c r="F281" s="7">
-        <v>91.9</v>
-      </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A282" s="26" t="s">
-        <v>202</v>
-      </c>
       <c r="B282" s="51"/>
       <c r="C282" s="52"/>
       <c r="D282" s="52"/>
       <c r="E282" s="53"/>
-      <c r="F282" s="7">
-        <v>98.9</v>
-      </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A283" s="26">
-        <v>1007</v>
-      </c>
       <c r="B283" s="51"/>
       <c r="C283" s="52"/>
       <c r="D283" s="52"/>
       <c r="E283" s="53"/>
-      <c r="F283" s="7">
-        <v>60.9</v>
-      </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A284" s="26">
-        <v>1008</v>
-      </c>
       <c r="B284" s="51"/>
       <c r="C284" s="52"/>
       <c r="D284" s="52"/>
       <c r="E284" s="53"/>
-      <c r="F284" s="7">
-        <v>87.9</v>
-      </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A285" s="26" t="s">
-        <v>203</v>
-      </c>
       <c r="B285" s="51"/>
       <c r="C285" s="52"/>
       <c r="D285" s="52"/>
       <c r="E285" s="53"/>
-      <c r="F285" s="7">
-        <v>94.9</v>
-      </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A286" s="26">
-        <v>1009</v>
-      </c>
       <c r="B286" s="51"/>
       <c r="C286" s="52"/>
       <c r="D286" s="52"/>
       <c r="E286" s="53"/>
-      <c r="F286" s="7">
-        <v>87.9</v>
-      </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A287" s="26" t="s">
-        <v>204</v>
-      </c>
       <c r="B287" s="51"/>
       <c r="C287" s="52"/>
       <c r="D287" s="52"/>
       <c r="E287" s="53"/>
-      <c r="F287" s="7">
-        <v>94.9</v>
-      </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A288" s="26">
-        <v>1010</v>
-      </c>
       <c r="B288" s="51"/>
       <c r="C288" s="52"/>
       <c r="D288" s="52"/>
       <c r="E288" s="53"/>
-      <c r="F288" s="7">
-        <v>36.9</v>
-      </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A289" s="26">
-        <v>1011</v>
-      </c>
       <c r="B289" s="51"/>
       <c r="C289" s="52"/>
       <c r="D289" s="52"/>
       <c r="E289" s="53"/>
-      <c r="F289" s="7">
-        <v>34</v>
-      </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A290" s="26">
-        <v>1012</v>
-      </c>
       <c r="B290" s="51"/>
       <c r="C290" s="52"/>
       <c r="D290" s="52"/>
       <c r="E290" s="53"/>
-      <c r="F290" s="7">
-        <v>37.9</v>
-      </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A291" s="26">
-        <v>1013</v>
-      </c>
       <c r="B291" s="51"/>
       <c r="C291" s="52"/>
       <c r="D291" s="52"/>
       <c r="E291" s="53"/>
-      <c r="F291" s="7">
-        <v>39.9</v>
-      </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A292" s="26">
-        <v>1020</v>
-      </c>
       <c r="B292" s="51"/>
       <c r="C292" s="52"/>
       <c r="D292" s="52"/>
       <c r="E292" s="53"/>
-      <c r="F292" s="7">
-        <v>65.900000000000006</v>
-      </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A293" s="26">
-        <v>1021</v>
-      </c>
       <c r="B293" s="51"/>
       <c r="C293" s="52"/>
       <c r="D293" s="52"/>
       <c r="E293" s="53"/>
-      <c r="F293" s="7">
-        <v>65.900000000000006</v>
-      </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A294" s="26">
-        <v>1023</v>
-      </c>
       <c r="B294" s="51"/>
       <c r="C294" s="52"/>
       <c r="D294" s="52"/>
       <c r="E294" s="53"/>
-      <c r="F294" s="7">
-        <v>60.9</v>
-      </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A295" s="26">
-        <v>1024</v>
-      </c>
       <c r="B295" s="51"/>
       <c r="C295" s="52"/>
       <c r="D295" s="52"/>
       <c r="E295" s="53"/>
-      <c r="F295" s="7">
-        <v>39.9</v>
-      </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A296" s="26">
-        <v>1025</v>
-      </c>
       <c r="B296" s="51"/>
       <c r="C296" s="52"/>
       <c r="D296" s="52"/>
       <c r="E296" s="53"/>
-      <c r="F296" s="7">
-        <v>60.9</v>
-      </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A297" s="26" t="s">
-        <v>205</v>
-      </c>
       <c r="B297" s="51"/>
       <c r="C297" s="52"/>
       <c r="D297" s="52"/>
       <c r="E297" s="53"/>
-      <c r="F297" s="7">
-        <v>65.900000000000006</v>
-      </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A298" s="26">
-        <v>1026</v>
-      </c>
       <c r="B298" s="51"/>
       <c r="C298" s="52"/>
       <c r="D298" s="52"/>
       <c r="E298" s="53"/>
-      <c r="F298" s="7">
-        <v>93.9</v>
-      </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A299" s="26" t="s">
-        <v>206</v>
-      </c>
       <c r="B299" s="51"/>
       <c r="C299" s="52"/>
       <c r="D299" s="52"/>
       <c r="E299" s="53"/>
-      <c r="F299" s="7">
-        <v>102.9</v>
-      </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A300" s="26">
-        <v>1027</v>
-      </c>
       <c r="B300" s="51"/>
       <c r="C300" s="52"/>
       <c r="D300" s="52"/>
       <c r="E300" s="53"/>
-      <c r="F300" s="7">
-        <v>97.9</v>
-      </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A301" s="26" t="s">
-        <v>207</v>
-      </c>
       <c r="B301" s="51"/>
       <c r="C301" s="52"/>
       <c r="D301" s="52"/>
       <c r="E301" s="53"/>
-      <c r="F301" s="7">
-        <v>106.9</v>
-      </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A302" s="26">
-        <v>1030</v>
-      </c>
       <c r="B302" s="51"/>
       <c r="C302" s="52"/>
       <c r="D302" s="52"/>
       <c r="E302" s="53"/>
-      <c r="F302" s="7">
-        <v>68.900000000000006</v>
-      </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A303" s="26" t="s">
-        <v>208</v>
-      </c>
       <c r="B303" s="51"/>
       <c r="C303" s="52"/>
       <c r="D303" s="52"/>
       <c r="E303" s="53"/>
-      <c r="F303" s="7">
-        <v>75.900000000000006</v>
-      </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A304" s="26">
-        <v>1031</v>
-      </c>
       <c r="B304" s="51"/>
       <c r="C304" s="52"/>
       <c r="D304" s="52"/>
       <c r="E304" s="53"/>
-      <c r="F304" s="7">
-        <v>60.9</v>
-      </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A305" s="26" t="s">
-        <v>209</v>
-      </c>
       <c r="B305" s="51"/>
       <c r="C305" s="52"/>
       <c r="D305" s="52"/>
       <c r="E305" s="53"/>
-      <c r="F305" s="7">
-        <v>65.900000000000006</v>
-      </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A306" s="26">
-        <v>1032</v>
-      </c>
       <c r="B306" s="51"/>
       <c r="C306" s="52"/>
       <c r="D306" s="52"/>
       <c r="E306" s="53"/>
-      <c r="F306" s="7">
-        <v>95.9</v>
-      </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A307" s="26" t="s">
-        <v>210</v>
-      </c>
       <c r="B307" s="51"/>
       <c r="C307" s="52"/>
       <c r="D307" s="52"/>
       <c r="E307" s="53"/>
-      <c r="F307" s="7">
-        <v>105.9</v>
-      </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A308" s="26">
-        <v>1033</v>
-      </c>
       <c r="B308" s="51"/>
       <c r="C308" s="52"/>
       <c r="D308" s="52"/>
       <c r="E308" s="53"/>
-      <c r="F308" s="7">
-        <v>60.9</v>
-      </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A309" s="26" t="s">
-        <v>211</v>
-      </c>
       <c r="B309" s="51"/>
       <c r="C309" s="52"/>
       <c r="D309" s="52"/>
       <c r="E309" s="53"/>
-      <c r="F309" s="7">
-        <v>65.900000000000006</v>
-      </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A310" s="26">
-        <v>1034</v>
-      </c>
       <c r="B310" s="51"/>
       <c r="C310" s="52"/>
       <c r="D310" s="52"/>
       <c r="E310" s="53"/>
-      <c r="F310" s="7">
-        <v>36.9</v>
-      </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A311" s="26" t="s">
-        <v>212</v>
-      </c>
       <c r="B311" s="51"/>
       <c r="C311" s="52"/>
       <c r="D311" s="52"/>
       <c r="E311" s="53"/>
-      <c r="F311" s="7">
-        <v>39.9</v>
-      </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A312" s="26">
-        <v>1035</v>
-      </c>
       <c r="B312" s="51"/>
       <c r="C312" s="52"/>
       <c r="D312" s="52"/>
       <c r="E312" s="53"/>
-      <c r="F312" s="7">
-        <v>41.9</v>
-      </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A313" s="26" t="s">
-        <v>215</v>
-      </c>
       <c r="B313" s="51"/>
       <c r="C313" s="52"/>
       <c r="D313" s="52"/>
       <c r="E313" s="53"/>
-      <c r="F313" s="7">
-        <v>45</v>
-      </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A314" s="26">
-        <v>1036</v>
-      </c>
       <c r="B314" s="51"/>
       <c r="C314" s="52"/>
       <c r="D314" s="52"/>
       <c r="E314" s="53"/>
-      <c r="F314" s="7">
-        <v>43.9</v>
-      </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A315" s="26">
-        <v>1037</v>
-      </c>
       <c r="B315" s="51"/>
       <c r="C315" s="52"/>
       <c r="D315" s="52"/>
       <c r="E315" s="53"/>
-      <c r="F315" s="7">
-        <v>54.9</v>
-      </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A316" s="26">
-        <v>1038</v>
-      </c>
       <c r="B316" s="51"/>
       <c r="C316" s="52"/>
       <c r="D316" s="52"/>
       <c r="E316" s="53"/>
-      <c r="F316" s="7">
-        <v>32.9</v>
-      </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A317" s="26">
-        <v>1039</v>
-      </c>
       <c r="B317" s="51"/>
       <c r="C317" s="52"/>
       <c r="D317" s="52"/>
       <c r="E317" s="53"/>
-      <c r="F317" s="7">
-        <v>36.9</v>
-      </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A318" s="26">
-        <v>1040</v>
-      </c>
       <c r="B318" s="51"/>
       <c r="C318" s="52"/>
       <c r="D318" s="52"/>
       <c r="E318" s="53"/>
-      <c r="F318" s="7">
-        <v>39.9</v>
-      </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A319" s="26">
-        <v>1041</v>
-      </c>
       <c r="B319" s="51"/>
       <c r="C319" s="52"/>
       <c r="D319" s="52"/>
       <c r="E319" s="53"/>
-      <c r="F319" s="7">
-        <v>39.9</v>
-      </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A320" s="26">
-        <v>1042</v>
-      </c>
       <c r="B320" s="51"/>
       <c r="C320" s="52"/>
       <c r="D320" s="52"/>
       <c r="E320" s="53"/>
-      <c r="F320" s="7">
-        <v>27.9</v>
-      </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A321" s="26" t="s">
-        <v>214</v>
-      </c>
       <c r="B321" s="51"/>
       <c r="C321" s="52"/>
       <c r="D321" s="52"/>
       <c r="E321" s="53"/>
-      <c r="F321" s="7">
-        <v>30.9</v>
-      </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A322" s="26">
-        <v>1043</v>
-      </c>
       <c r="B322" s="51"/>
       <c r="C322" s="52"/>
       <c r="D322" s="52"/>
       <c r="E322" s="53"/>
-      <c r="F322" s="7">
-        <v>30.9</v>
-      </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A323" s="26" t="s">
-        <v>213</v>
-      </c>
       <c r="B323" s="51"/>
       <c r="C323" s="52"/>
       <c r="D323" s="52"/>
       <c r="E323" s="53"/>
-      <c r="F323" s="7">
-        <v>34</v>
-      </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A324" s="26">
-        <v>1400</v>
-      </c>
       <c r="B324" s="51"/>
       <c r="C324" s="52"/>
       <c r="D324" s="52"/>
       <c r="E324" s="53"/>
-      <c r="F324" s="7">
-        <v>40.9</v>
-      </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A325" s="26">
-        <v>1460</v>
-      </c>
       <c r="B325" s="51"/>
       <c r="C325" s="52"/>
       <c r="D325" s="52"/>
       <c r="E325" s="53"/>
-      <c r="F325" s="7">
-        <v>42.9</v>
-      </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A326" s="26">
-        <v>2014</v>
-      </c>
       <c r="B326" s="51" t="s">
         <v>156</v>
       </c>
       <c r="C326" s="52"/>
       <c r="D326" s="52"/>
       <c r="E326" s="53"/>
-      <c r="F326" s="7">
-        <v>14.9</v>
-      </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A327" s="26">
-        <v>2130</v>
-      </c>
       <c r="B327" s="51"/>
       <c r="C327" s="52"/>
       <c r="D327" s="52"/>
       <c r="E327" s="53"/>
-      <c r="F327" s="7">
-        <v>54.9</v>
-      </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A328" s="26" t="s">
-        <v>146</v>
-      </c>
       <c r="B328" s="51"/>
       <c r="C328" s="52"/>
       <c r="D328" s="52"/>
       <c r="E328" s="53"/>
-      <c r="F328" s="7">
-        <v>59.9</v>
-      </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A329" s="26">
-        <v>2131</v>
-      </c>
       <c r="B329" s="51"/>
       <c r="C329" s="52"/>
       <c r="D329" s="52"/>
       <c r="E329" s="53"/>
-      <c r="F329" s="7">
-        <v>37.9</v>
-      </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A330" s="26" t="s">
-        <v>147</v>
-      </c>
       <c r="B330" s="51"/>
       <c r="C330" s="52"/>
       <c r="D330" s="52"/>
       <c r="E330" s="53"/>
-      <c r="F330" s="7">
-        <v>40.9</v>
-      </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A331" s="26">
-        <v>2134</v>
-      </c>
       <c r="B331" s="51"/>
       <c r="C331" s="52"/>
       <c r="D331" s="52"/>
       <c r="E331" s="53"/>
-      <c r="F331" s="7">
-        <v>37.9</v>
-      </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A332" s="26" t="s">
-        <v>148</v>
-      </c>
       <c r="B332" s="51"/>
       <c r="C332" s="52"/>
       <c r="D332" s="52"/>
       <c r="E332" s="53"/>
-      <c r="F332" s="7">
-        <v>40.9</v>
-      </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A333" s="26">
-        <v>2226</v>
-      </c>
       <c r="B333" s="51"/>
       <c r="C333" s="52"/>
       <c r="D333" s="52"/>
       <c r="E333" s="53"/>
-      <c r="F333" s="7">
-        <v>43.9</v>
-      </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A334" s="26" t="s">
-        <v>149</v>
-      </c>
       <c r="B334" s="51"/>
       <c r="C334" s="52"/>
       <c r="D334" s="52"/>
       <c r="E334" s="53"/>
-      <c r="F334" s="7">
-        <v>48.9</v>
-      </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A335" s="26">
-        <v>4130</v>
-      </c>
       <c r="B335" s="51"/>
       <c r="C335" s="52"/>
       <c r="D335" s="52"/>
       <c r="E335" s="53"/>
-      <c r="F335" s="7">
-        <v>59.9</v>
-      </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A336" s="26" t="s">
-        <v>150</v>
-      </c>
       <c r="B336" s="51"/>
       <c r="C336" s="52"/>
       <c r="D336" s="52"/>
       <c r="E336" s="53"/>
-      <c r="F336" s="7">
-        <v>65.5</v>
-      </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A337" s="26">
-        <v>4131</v>
-      </c>
       <c r="B337" s="51"/>
       <c r="C337" s="52"/>
       <c r="D337" s="52"/>
       <c r="E337" s="53"/>
-      <c r="F337" s="7">
-        <v>62.9</v>
-      </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A338" s="26" t="s">
-        <v>151</v>
-      </c>
       <c r="B338" s="51"/>
       <c r="C338" s="52"/>
       <c r="D338" s="52"/>
       <c r="E338" s="53"/>
-      <c r="F338" s="7">
-        <v>68.900000000000006</v>
-      </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A339" s="10"/>
       <c r="B339" s="4"/>
       <c r="C339" s="19"/>
       <c r="D339" s="19"/>
       <c r="E339" s="15"/>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A340" s="10"/>
       <c r="B340" s="4"/>
       <c r="C340" s="19"/>
       <c r="D340" s="19"/>
       <c r="E340" s="15"/>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A341" s="10"/>
       <c r="B341" s="4"/>
       <c r="C341" s="19"/>
       <c r="D341" s="19"/>
       <c r="E341" s="15"/>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A342" s="10"/>
       <c r="B342" s="4"/>
       <c r="C342" s="19"/>
       <c r="D342" s="19"/>
       <c r="E342" s="15"/>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A343" s="10"/>
       <c r="B343" s="4"/>
       <c r="C343" s="19"/>
       <c r="D343" s="19"/>
       <c r="E343" s="15"/>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A344" s="10"/>
       <c r="B344" s="4"/>
       <c r="C344" s="19"/>
       <c r="D344" s="19"/>
       <c r="E344" s="15"/>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A345" s="10"/>
       <c r="B345" s="4"/>
       <c r="C345" s="19"/>
       <c r="D345" s="19"/>
       <c r="E345" s="15"/>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A346" s="10"/>
       <c r="B346" s="4"/>
       <c r="C346" s="19"/>
       <c r="D346" s="19"/>
       <c r="E346" s="15"/>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A347" s="10"/>
       <c r="B347" s="4"/>
       <c r="C347" s="19"/>
       <c r="D347" s="19"/>
       <c r="E347" s="15"/>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A348" s="8"/>
       <c r="B348" s="4"/>
       <c r="C348" s="19"/>
       <c r="D348" s="19"/>
       <c r="E348" s="15"/>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A349" s="8"/>
       <c r="B349" s="4"/>
       <c r="C349" s="19"/>
       <c r="D349" s="19"/>
       <c r="E349" s="15"/>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A350" s="8"/>
       <c r="B350" s="4"/>
       <c r="C350" s="19"/>
       <c r="D350" s="19"/>
       <c r="E350" s="15"/>
-      <c r="F350" s="6"/>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A351" s="8"/>
       <c r="B351" s="4"/>
       <c r="C351" s="19"/>
       <c r="D351" s="19"/>
       <c r="E351" s="15"/>
-      <c r="F351" s="6"/>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A352" s="8"/>
       <c r="B352" s="4"/>
       <c r="C352" s="19"/>
       <c r="D352" s="19"/>
       <c r="E352" s="15"/>
-      <c r="F352" s="6"/>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A353" s="8"/>
       <c r="B353" s="4"/>
       <c r="C353" s="19"/>
       <c r="D353" s="19"/>
       <c r="E353" s="15"/>
-      <c r="F353" s="6"/>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A354" s="8"/>
       <c r="B354" s="4"/>
       <c r="C354" s="19"/>
       <c r="D354" s="19"/>
       <c r="E354" s="15"/>
-      <c r="F354" s="6"/>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A355" s="8"/>
       <c r="B355" s="4"/>
       <c r="C355" s="19"/>
       <c r="D355" s="19"/>
       <c r="E355" s="15"/>
-      <c r="F355" s="6"/>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A356" s="8"/>
       <c r="B356" s="2"/>
       <c r="C356" s="19"/>
       <c r="D356" s="19"/>
       <c r="E356" s="15"/>
-      <c r="F356" s="6"/>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A357" s="8"/>
       <c r="B357" s="2"/>
       <c r="C357" s="19"/>
       <c r="D357" s="19"/>
       <c r="E357" s="15"/>
-      <c r="F357" s="6"/>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A358" s="8"/>
       <c r="B358" s="2"/>
       <c r="C358" s="19"/>
       <c r="D358" s="19"/>
       <c r="E358" s="15"/>
-      <c r="F358" s="6"/>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A359" s="8"/>
       <c r="B359" s="2"/>
       <c r="C359" s="19"/>
       <c r="D359" s="19"/>
       <c r="E359" s="15"/>
-      <c r="F359" s="6"/>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A360" s="8"/>
       <c r="B360" s="2"/>
       <c r="C360" s="19"/>
       <c r="D360" s="19"/>
       <c r="E360" s="15"/>
-      <c r="F360" s="6"/>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A361" s="8"/>
       <c r="B361" s="2"/>
       <c r="C361" s="19"/>
       <c r="D361" s="19"/>
       <c r="E361" s="15"/>
-      <c r="F361" s="6"/>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A362" s="8"/>
       <c r="B362" s="3"/>
       <c r="C362" s="19"/>
       <c r="D362" s="19"/>
       <c r="E362" s="15"/>
-      <c r="F362" s="6"/>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A363" s="8"/>
       <c r="B363" s="3"/>
       <c r="C363" s="19"/>
       <c r="D363" s="19"/>
       <c r="E363" s="15"/>
-      <c r="F363" s="6"/>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A364" s="8"/>
       <c r="B364" s="3"/>
       <c r="C364" s="19"/>
       <c r="D364" s="19"/>
       <c r="E364" s="15"/>
-      <c r="F364" s="6"/>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A365" s="8"/>
       <c r="B365" s="3"/>
       <c r="C365" s="19"/>
       <c r="D365" s="19"/>
       <c r="E365" s="15"/>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A366" s="8"/>
       <c r="B366" s="3"/>
       <c r="C366" s="19"/>
       <c r="D366" s="19"/>
       <c r="E366" s="15"/>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A367" s="8"/>
       <c r="B367" s="3"/>
       <c r="C367" s="19"/>
       <c r="D367" s="19"/>
       <c r="E367" s="15"/>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A368" s="8"/>
       <c r="B368" s="3"/>
       <c r="C368" s="19"/>
       <c r="D368" s="19"/>
       <c r="E368" s="15"/>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A369" s="8"/>
       <c r="B369" s="3"/>
       <c r="C369" s="19"/>
       <c r="D369" s="19"/>
       <c r="E369" s="15"/>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A370" s="8"/>
       <c r="B370" s="3"/>
       <c r="C370" s="19"/>
       <c r="D370" s="19"/>
       <c r="E370" s="15"/>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A371" s="8"/>
       <c r="B371" s="3"/>
       <c r="C371" s="20"/>
       <c r="D371" s="20"/>
       <c r="E371" s="16"/>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A372" s="8"/>
       <c r="B372" s="3"/>
       <c r="C372" s="19"/>
       <c r="D372" s="19"/>
       <c r="E372" s="15"/>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A373" s="8"/>
       <c r="B373" s="3"/>
       <c r="C373" s="19"/>
       <c r="D373" s="19"/>
       <c r="E373" s="15"/>
-      <c r="F373" s="6"/>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A374" s="8"/>
       <c r="B374" s="3"/>
       <c r="C374" s="19"/>
       <c r="D374" s="19"/>
       <c r="E374" s="15"/>
-      <c r="F374" s="6"/>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A375" s="8"/>
       <c r="B375" s="3"/>
       <c r="C375" s="19"/>
       <c r="D375" s="19"/>
       <c r="E375" s="15"/>
-      <c r="F375" s="6"/>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A376" s="8"/>
       <c r="B376" s="3"/>
       <c r="C376" s="19"/>
       <c r="D376" s="19"/>
       <c r="E376" s="15"/>
-      <c r="F376" s="6"/>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A377" s="8"/>
       <c r="B377" s="3"/>
       <c r="C377" s="19"/>
       <c r="D377" s="19"/>
       <c r="E377" s="15"/>
-      <c r="F377" s="6"/>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A378" s="8"/>
       <c r="B378" s="3"/>
       <c r="C378" s="19"/>
       <c r="D378" s="19"/>
       <c r="E378" s="15"/>
-      <c r="F378" s="6"/>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A379" s="8"/>
       <c r="B379" s="3"/>
       <c r="C379" s="19"/>
       <c r="D379" s="19"/>
       <c r="E379" s="15"/>
-      <c r="F379" s="6"/>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A380" s="9"/>
       <c r="B380" s="3"/>
       <c r="C380" s="19"/>
       <c r="D380" s="19"/>
       <c r="E380" s="15"/>
-      <c r="F380" s="6"/>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A381" s="8"/>
       <c r="B381" s="3"/>
       <c r="C381" s="19"/>
       <c r="D381" s="19"/>
       <c r="E381" s="15"/>
-      <c r="F381" s="6"/>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A382" s="8"/>
       <c r="B382" s="3"/>
       <c r="C382" s="19"/>
       <c r="D382" s="19"/>
       <c r="E382" s="15"/>
-      <c r="F382" s="6"/>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A383" s="8"/>
       <c r="B383" s="3"/>
       <c r="C383" s="19"/>
       <c r="D383" s="19"/>
       <c r="E383" s="15"/>
-      <c r="F383" s="6"/>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A384" s="8"/>
       <c r="B384" s="3"/>
       <c r="C384" s="19"/>
       <c r="D384" s="19"/>
       <c r="E384" s="15"/>
-      <c r="F384" s="6"/>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A385" s="8"/>
       <c r="B385" s="3"/>
       <c r="C385" s="19"/>
       <c r="D385" s="19"/>
       <c r="E385" s="15"/>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A386" s="8"/>
       <c r="B386" s="3"/>
       <c r="C386" s="19"/>
       <c r="D386" s="19"/>
       <c r="E386" s="15"/>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A387" s="8"/>
       <c r="B387" s="3"/>
       <c r="C387" s="19"/>
       <c r="D387" s="19"/>
       <c r="E387" s="15"/>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A388" s="8"/>
       <c r="B388" s="3"/>
       <c r="C388" s="19"/>
       <c r="D388" s="19"/>
       <c r="E388" s="15"/>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A389" s="8"/>
       <c r="B389" s="3"/>
       <c r="C389" s="19"/>
       <c r="D389" s="19"/>
       <c r="E389" s="15"/>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A390" s="8"/>
       <c r="B390" s="3"/>
       <c r="C390" s="19"/>
       <c r="D390" s="19"/>
       <c r="E390" s="15"/>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A391" s="8"/>
       <c r="B391" s="3"/>
       <c r="C391" s="19"/>
       <c r="D391" s="19"/>
       <c r="E391" s="15"/>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A392" s="8"/>
       <c r="B392" s="3"/>
       <c r="C392" s="19"/>
       <c r="D392" s="19"/>
       <c r="E392" s="15"/>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A393" s="8"/>
       <c r="B393" s="3"/>
       <c r="C393" s="19"/>
       <c r="D393" s="19"/>
       <c r="E393" s="15"/>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A394" s="8"/>
       <c r="B394" s="3"/>
       <c r="C394" s="19"/>
       <c r="D394" s="19"/>
       <c r="E394" s="15"/>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A395" s="8"/>
       <c r="B395" s="3"/>
       <c r="C395" s="19"/>
       <c r="D395" s="19"/>
       <c r="E395" s="15"/>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A396" s="8"/>
       <c r="B396" s="3"/>
       <c r="C396" s="19"/>
       <c r="D396" s="19"/>
       <c r="E396" s="15"/>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A397" s="8"/>
       <c r="B397" s="3"/>
       <c r="C397" s="19"/>
       <c r="D397" s="19"/>
       <c r="E397" s="15"/>
-      <c r="F397" s="6"/>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A398" s="8"/>
       <c r="B398" s="3"/>
       <c r="C398" s="19"/>
       <c r="D398" s="19"/>
       <c r="E398" s="15"/>
-      <c r="F398" s="6"/>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A399" s="8"/>
       <c r="B399" s="3"/>
       <c r="C399" s="19"/>
       <c r="D399" s="19"/>
       <c r="E399" s="15"/>
-      <c r="F399" s="6"/>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A400" s="8"/>
       <c r="B400" s="3"/>
       <c r="C400" s="19"/>
       <c r="D400" s="19"/>
       <c r="E400" s="15"/>
-      <c r="F400" s="6"/>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A401" s="8"/>
       <c r="B401" s="3"/>
       <c r="C401" s="19"/>
       <c r="D401" s="19"/>
       <c r="E401" s="15"/>
-      <c r="F401" s="6"/>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A402" s="8"/>
       <c r="B402" s="3"/>
       <c r="C402" s="19"/>
       <c r="D402" s="19"/>
       <c r="E402" s="15"/>
-      <c r="F402" s="6"/>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A403" s="8"/>
       <c r="B403" s="3"/>
       <c r="C403" s="19"/>
       <c r="D403" s="19"/>
       <c r="E403" s="15"/>
-      <c r="F403" s="6"/>
     </row>
     <row r="404" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A404" s="8"/>
       <c r="B404" s="3"/>
       <c r="C404" s="19"/>
       <c r="D404" s="19"/>
       <c r="E404" s="15"/>
-      <c r="F404" s="13"/>
     </row>
     <row r="405" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A405" s="8"/>
       <c r="B405" s="3"/>
       <c r="C405" s="19"/>
       <c r="D405" s="19"/>
       <c r="E405" s="15"/>
-      <c r="F405" s="13"/>
     </row>
     <row r="406" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A406" s="8"/>
       <c r="B406" s="3"/>
       <c r="C406" s="19"/>
       <c r="D406" s="19"/>
       <c r="E406" s="15"/>
-      <c r="F406" s="13"/>
     </row>
     <row r="407" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A407" s="8"/>
       <c r="B407" s="3"/>
       <c r="C407" s="19"/>
       <c r="D407" s="19"/>
       <c r="E407" s="15"/>
-      <c r="F407" s="13"/>
     </row>
     <row r="408" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A408" s="8"/>
       <c r="B408" s="3"/>
       <c r="C408" s="19"/>
       <c r="D408" s="19"/>
       <c r="E408" s="15"/>
-      <c r="F408" s="13"/>
     </row>
     <row r="409" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A409" s="8"/>
       <c r="B409" s="3"/>
       <c r="C409" s="19"/>
       <c r="D409" s="19"/>
       <c r="E409" s="15"/>
-      <c r="F409" s="13"/>
     </row>
     <row r="410" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A410" s="8"/>
       <c r="B410" s="3"/>
       <c r="C410" s="19"/>
       <c r="D410" s="19"/>
       <c r="E410" s="15"/>
-      <c r="F410" s="13"/>
     </row>
     <row r="411" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A411" s="8"/>
       <c r="B411" s="3"/>
       <c r="C411" s="19"/>
       <c r="D411" s="19"/>
       <c r="E411" s="15"/>
-      <c r="F411" s="14"/>
     </row>
     <row r="412" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A412" s="8"/>
       <c r="B412" s="3"/>
       <c r="C412" s="19"/>
       <c r="D412" s="19"/>
       <c r="E412" s="15"/>
-      <c r="F412" s="14"/>
     </row>
     <row r="413" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A413" s="8"/>
       <c r="B413" s="3"/>
       <c r="C413" s="19"/>
       <c r="D413" s="19"/>
       <c r="E413" s="15"/>
-      <c r="F413" s="14"/>
     </row>
     <row r="414" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A414" s="8"/>
       <c r="B414" s="3"/>
       <c r="C414" s="19"/>
       <c r="D414" s="19"/>
       <c r="E414" s="15"/>
-      <c r="F414" s="14"/>
     </row>
     <row r="415" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A415" s="8"/>
       <c r="B415" s="3"/>
       <c r="C415" s="19"/>
       <c r="D415" s="19"/>
       <c r="E415" s="15"/>
-      <c r="F415" s="14"/>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A416" s="8"/>
       <c r="B416" s="3"/>
       <c r="C416" s="21"/>
       <c r="D416" s="21"/>
       <c r="E416" s="17"/>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A417" s="8"/>
       <c r="B417" s="3"/>
       <c r="C417" s="21"/>
       <c r="D417" s="21"/>
       <c r="E417" s="17"/>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A418" s="8"/>
       <c r="B418" s="3"/>
       <c r="C418" s="21"/>
       <c r="D418" s="21"/>
       <c r="E418" s="17"/>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A419" s="8"/>
       <c r="B419" s="3"/>
       <c r="C419" s="21"/>
       <c r="D419" s="21"/>
       <c r="E419" s="17"/>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A420" s="8"/>
       <c r="B420" s="3"/>
       <c r="C420" s="21"/>
       <c r="D420" s="21"/>
       <c r="E420" s="17"/>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A421" s="8"/>
       <c r="B421" s="3"/>
       <c r="C421" s="21"/>
       <c r="D421" s="21"/>
       <c r="E421" s="17"/>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A422" s="8"/>
       <c r="B422" s="3"/>
       <c r="C422" s="21"/>
       <c r="D422" s="21"/>
       <c r="E422" s="17"/>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A423" s="8"/>
       <c r="B423" s="3"/>
       <c r="C423" s="21"/>
       <c r="D423" s="21"/>
       <c r="E423" s="17"/>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A424" s="8"/>
       <c r="B424" s="3"/>
       <c r="C424" s="21"/>
       <c r="D424" s="21"/>
       <c r="E424" s="17"/>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A425" s="8"/>
       <c r="B425" s="3"/>
       <c r="C425" s="21"/>
       <c r="D425" s="21"/>
       <c r="E425" s="17"/>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A426" s="8"/>
       <c r="B426" s="3"/>
       <c r="C426" s="21"/>
       <c r="D426" s="21"/>
       <c r="E426" s="17"/>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A427" s="8"/>
       <c r="B427" s="3"/>
       <c r="C427" s="21"/>
       <c r="D427" s="21"/>
       <c r="E427" s="17"/>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A428" s="8"/>
       <c r="B428" s="3"/>
       <c r="C428" s="21"/>
       <c r="D428" s="21"/>
       <c r="E428" s="17"/>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A429" s="8"/>
       <c r="B429" s="3"/>
       <c r="C429" s="21"/>
       <c r="D429" s="21"/>
       <c r="E429" s="17"/>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A430" s="8"/>
       <c r="B430" s="3"/>
       <c r="C430" s="21"/>
       <c r="D430" s="21"/>
       <c r="E430" s="17"/>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A431" s="8"/>
       <c r="B431" s="3"/>
       <c r="C431" s="21"/>
       <c r="D431" s="21"/>
       <c r="E431" s="17"/>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A432" s="8"/>
       <c r="B432" s="3"/>
       <c r="C432" s="21"/>
       <c r="D432" s="21"/>
       <c r="E432" s="17"/>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A433" s="8"/>
       <c r="B433" s="3"/>
       <c r="C433" s="21"/>
       <c r="D433" s="21"/>
       <c r="E433" s="17"/>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A434" s="8"/>
       <c r="B434" s="3"/>
       <c r="C434" s="21"/>
       <c r="D434" s="21"/>
       <c r="E434" s="17"/>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A435" s="8"/>
       <c r="B435" s="3"/>
       <c r="C435" s="21"/>
       <c r="D435" s="21"/>
       <c r="E435" s="17"/>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A436" s="8"/>
       <c r="B436" s="3"/>
       <c r="C436" s="21"/>
       <c r="D436" s="21"/>
       <c r="E436" s="17"/>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A437" s="8"/>
       <c r="B437" s="3"/>
       <c r="C437" s="21"/>
       <c r="D437" s="21"/>
       <c r="E437" s="17"/>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A438" s="8"/>
       <c r="B438" s="3"/>
       <c r="C438" s="21"/>
       <c r="D438" s="21"/>
       <c r="E438" s="17"/>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A439" s="8"/>
       <c r="B439" s="3"/>
       <c r="C439" s="21"/>
       <c r="D439" s="21"/>
       <c r="E439" s="17"/>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A440" s="8"/>
       <c r="B440" s="3"/>
       <c r="C440" s="21"/>
       <c r="D440" s="21"/>
       <c r="E440" s="17"/>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A441" s="8"/>
       <c r="B441" s="3"/>
       <c r="C441" s="21"/>
       <c r="D441" s="21"/>
       <c r="E441" s="17"/>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A442" s="8"/>
       <c r="B442" s="3"/>
       <c r="C442" s="21"/>
       <c r="D442" s="21"/>
       <c r="E442" s="17"/>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A443" s="8"/>
       <c r="B443" s="3"/>
       <c r="C443" s="21"/>
       <c r="D443" s="21"/>
       <c r="E443" s="17"/>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A444" s="8"/>
       <c r="B444" s="3"/>
       <c r="C444" s="21"/>
       <c r="D444" s="21"/>
       <c r="E444" s="17"/>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A445" s="8"/>
       <c r="B445" s="3"/>
       <c r="C445" s="21"/>
       <c r="D445" s="21"/>
       <c r="E445" s="17"/>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A446" s="8"/>
       <c r="B446" s="3"/>
       <c r="C446" s="21"/>
       <c r="D446" s="21"/>
       <c r="E446" s="17"/>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A447" s="8"/>
       <c r="B447" s="3"/>
       <c r="C447" s="21"/>
       <c r="D447" s="21"/>
       <c r="E447" s="17"/>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A448" s="8"/>
       <c r="B448" s="3"/>
       <c r="C448" s="21"/>
       <c r="D448" s="21"/>
       <c r="E448" s="17"/>
-    </row>
-    <row r="449" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A449" s="8"/>
-    </row>
-    <row r="450" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A450" s="8"/>
-    </row>
-    <row r="451" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A451" s="8"/>
-    </row>
-    <row r="452" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A452" s="8"/>
-    </row>
-    <row r="453" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A453" s="8"/>
-    </row>
-    <row r="454" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A454" s="8"/>
-    </row>
-    <row r="455" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A455" s="8"/>
-    </row>
-    <row r="456" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A456" s="8"/>
-    </row>
-    <row r="457" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A457" s="8"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="qrwFUFm2emZ0XjtlNuBuyXzu5+zjVB/6wrCb+OfLBd89OB7dlApks5AHxEIqU8MmCnH2KD9CUPBMOo5il/uAYQ==" saltValue="cdBQlob+Fm2w3tHvGj3uSQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>

--- a/apps/web/public/modelos/pedido-cs-2.xlsx
+++ b/apps/web/public/modelos/pedido-cs-2.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11910"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="2" r:id="rId1"/>
@@ -2877,9 +2877,7 @@
       <c r="AG12" s="77"/>
     </row>
     <row r="13" spans="1:33" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="93">
-        <v>22238</v>
-      </c>
+      <c r="A13" s="93"/>
       <c r="B13" s="98"/>
       <c r="C13" s="98"/>
       <c r="D13" s="98"/>
@@ -2891,18 +2889,10 @@
       <c r="J13" s="98"/>
       <c r="K13" s="98"/>
       <c r="L13" s="44"/>
-      <c r="M13" s="44">
-        <v>2</v>
-      </c>
-      <c r="N13" s="36">
-        <v>3</v>
-      </c>
-      <c r="O13" s="36">
-        <v>2</v>
-      </c>
-      <c r="P13" s="36">
-        <v>2</v>
-      </c>
+      <c r="M13" s="44"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
       <c r="Q13" s="36"/>
       <c r="R13" s="36"/>
       <c r="S13" s="36"/>
@@ -2914,15 +2904,15 @@
       <c r="Y13" s="45"/>
       <c r="Z13" s="46">
         <f t="shared" ref="Z13:Z44" si="0">L13+M13+N13+O13+P13+U13+V13+W13+X13+Q13+R13+S13+T13</f>
-        <v>9</v>
-      </c>
-      <c r="AA13" s="27">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="27" t="str">
         <f>IFERROR(VLOOKUP(A13,Plan2!$A$1:$F$777,6,0),"-")</f>
-        <v>63.9</v>
-      </c>
-      <c r="AB13" s="43">
+        <v>-</v>
+      </c>
+      <c r="AB13" s="43" t="str">
         <f>IFERROR(AA13*Z13,"-")</f>
-        <v>575.1</v>
+        <v>-</v>
       </c>
       <c r="AE13" s="17"/>
       <c r="AF13" s="7" t="s">
@@ -2931,9 +2921,7 @@
       <c r="AG13" s="33"/>
     </row>
     <row r="14" spans="1:33" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="94">
-        <v>22126</v>
-      </c>
+      <c r="A14" s="94"/>
       <c r="B14" s="98"/>
       <c r="C14" s="98"/>
       <c r="D14" s="98"/>
@@ -2945,15 +2933,9 @@
       <c r="J14" s="98"/>
       <c r="K14" s="98"/>
       <c r="L14" s="44"/>
-      <c r="M14" s="47">
-        <v>2</v>
-      </c>
-      <c r="N14" s="38">
-        <v>3</v>
-      </c>
-      <c r="O14" s="38">
-        <v>2</v>
-      </c>
+      <c r="M14" s="47"/>
+      <c r="N14" s="38"/>
+      <c r="O14" s="38"/>
       <c r="P14" s="38"/>
       <c r="Q14" s="38"/>
       <c r="R14" s="38"/>
@@ -2966,15 +2948,15 @@
       <c r="Y14" s="40"/>
       <c r="Z14" s="41">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="AA14" s="42">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="42" t="str">
         <f>IFERROR(VLOOKUP(A14,Plan2!$A$1:$F$777,6,0),"-")</f>
-        <v>64.900000000000006</v>
-      </c>
-      <c r="AB14" s="43">
+        <v>-</v>
+      </c>
+      <c r="AB14" s="43" t="str">
         <f>IFERROR(AA14*Z14,"-")</f>
-        <v>454.30000000000007</v>
+        <v>-</v>
       </c>
       <c r="AF14" s="7">
         <v>87</v>
@@ -2982,9 +2964,7 @@
       <c r="AG14" s="33"/>
     </row>
     <row r="15" spans="1:33" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="95">
-        <v>22128</v>
-      </c>
+      <c r="A15" s="95"/>
       <c r="B15" s="98"/>
       <c r="C15" s="98"/>
       <c r="D15" s="98"/>
@@ -2996,18 +2976,10 @@
       <c r="J15" s="98"/>
       <c r="K15" s="98"/>
       <c r="L15" s="44"/>
-      <c r="M15" s="48">
-        <v>2</v>
-      </c>
-      <c r="N15" s="36">
-        <v>3</v>
-      </c>
-      <c r="O15" s="36">
-        <v>2</v>
-      </c>
-      <c r="P15" s="36">
-        <v>2</v>
-      </c>
+      <c r="M15" s="48"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
       <c r="Q15" s="36"/>
       <c r="R15" s="36"/>
       <c r="S15" s="36"/>
@@ -3019,15 +2991,15 @@
       <c r="Y15" s="26"/>
       <c r="Z15" s="32">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AA15" s="27">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="27" t="str">
         <f>IFERROR(VLOOKUP(A15,Plan2!$A$1:$F$777,6,0),"-")</f>
-        <v>60.9</v>
-      </c>
-      <c r="AB15" s="28">
+        <v>-</v>
+      </c>
+      <c r="AB15" s="28" t="str">
         <f t="shared" ref="AB15:AB44" si="1">IFERROR(AA15*Z15,"-")</f>
-        <v>548.1</v>
+        <v>-</v>
       </c>
       <c r="AF15" s="8" t="s">
         <v>53</v>
@@ -3035,9 +3007,7 @@
       <c r="AG15" s="33"/>
     </row>
     <row r="16" spans="1:33" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="95">
-        <v>22243</v>
-      </c>
+      <c r="A16" s="95"/>
       <c r="B16" s="98"/>
       <c r="C16" s="98"/>
       <c r="D16" s="98"/>
@@ -3049,18 +3019,10 @@
       <c r="J16" s="98"/>
       <c r="K16" s="98"/>
       <c r="L16" s="44"/>
-      <c r="M16" s="48">
-        <v>2</v>
-      </c>
-      <c r="N16" s="36">
-        <v>3</v>
-      </c>
-      <c r="O16" s="36">
-        <v>2</v>
-      </c>
-      <c r="P16" s="36">
-        <v>2</v>
-      </c>
+      <c r="M16" s="48"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
       <c r="Q16" s="36"/>
       <c r="R16" s="36"/>
       <c r="S16" s="36"/>
@@ -3072,15 +3034,15 @@
       <c r="Y16" s="26"/>
       <c r="Z16" s="32">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="AA16" s="27">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="27" t="str">
         <f>IFERROR(VLOOKUP(A16,Plan2!$A$1:$F$777,6,0),"-")</f>
-        <v>60.9</v>
-      </c>
-      <c r="AB16" s="28">
+        <v>-</v>
+      </c>
+      <c r="AB16" s="28" t="str">
         <f t="shared" si="1"/>
-        <v>548.1</v>
+        <v>-</v>
       </c>
       <c r="AF16" s="7">
         <v>88</v>
@@ -3088,9 +3050,7 @@
       <c r="AG16" s="33"/>
     </row>
     <row r="17" spans="1:33" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="95">
-        <v>2213</v>
-      </c>
+      <c r="A17" s="95"/>
       <c r="B17" s="98"/>
       <c r="C17" s="98"/>
       <c r="D17" s="98"/>
@@ -3102,18 +3062,10 @@
       <c r="J17" s="98"/>
       <c r="K17" s="98"/>
       <c r="L17" s="44"/>
-      <c r="M17" s="48">
-        <v>1</v>
-      </c>
-      <c r="N17" s="36">
-        <v>1</v>
-      </c>
-      <c r="O17" s="36">
-        <v>1</v>
-      </c>
-      <c r="P17" s="36">
-        <v>1</v>
-      </c>
+      <c r="M17" s="48"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
       <c r="Q17" s="36"/>
       <c r="R17" s="36"/>
       <c r="S17" s="36"/>
@@ -3125,15 +3077,15 @@
       <c r="Y17" s="26"/>
       <c r="Z17" s="32">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AA17" s="27">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="27" t="str">
         <f>IFERROR(VLOOKUP(A17,Plan2!$A$1:$F$777,6,0),"-")</f>
-        <v>65.900000000000006</v>
-      </c>
-      <c r="AB17" s="28">
+        <v>-</v>
+      </c>
+      <c r="AB17" s="28" t="str">
         <f t="shared" si="1"/>
-        <v>263.60000000000002</v>
+        <v>-</v>
       </c>
       <c r="AF17" s="7" t="s">
         <v>54</v>
@@ -3141,9 +3093,7 @@
       <c r="AG17" s="33"/>
     </row>
     <row r="18" spans="1:33" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="95">
-        <v>2279</v>
-      </c>
+      <c r="A18" s="95"/>
       <c r="B18" s="98"/>
       <c r="C18" s="98"/>
       <c r="D18" s="98"/>
@@ -3156,15 +3106,9 @@
       <c r="K18" s="98"/>
       <c r="L18" s="44"/>
       <c r="M18" s="48"/>
-      <c r="N18" s="36">
-        <v>2</v>
-      </c>
-      <c r="O18" s="36">
-        <v>2</v>
-      </c>
-      <c r="P18" s="36">
-        <v>2</v>
-      </c>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
       <c r="Q18" s="36"/>
       <c r="R18" s="36"/>
       <c r="S18" s="36"/>
@@ -3176,15 +3120,15 @@
       <c r="Y18" s="26"/>
       <c r="Z18" s="32">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="AA18" s="27">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="27" t="str">
         <f>IFERROR(VLOOKUP(A18,Plan2!$A$1:$F$777,6,0),"-")</f>
-        <v>72.900000000000006</v>
-      </c>
-      <c r="AB18" s="28">
+        <v>-</v>
+      </c>
+      <c r="AB18" s="28" t="str">
         <f t="shared" si="1"/>
-        <v>437.40000000000003</v>
+        <v>-</v>
       </c>
       <c r="AF18" s="7">
         <v>90</v>
@@ -3192,9 +3136,7 @@
       <c r="AG18" s="33"/>
     </row>
     <row r="19" spans="1:33" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="95">
-        <v>2215</v>
-      </c>
+      <c r="A19" s="95"/>
       <c r="B19" s="98"/>
       <c r="C19" s="98"/>
       <c r="D19" s="98"/>
@@ -3207,15 +3149,9 @@
       <c r="K19" s="98"/>
       <c r="L19" s="44"/>
       <c r="M19" s="48"/>
-      <c r="N19" s="36">
-        <v>1</v>
-      </c>
-      <c r="O19" s="36">
-        <v>2</v>
-      </c>
-      <c r="P19" s="36">
-        <v>1</v>
-      </c>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
       <c r="Q19" s="36"/>
       <c r="R19" s="36"/>
       <c r="S19" s="36"/>
@@ -3227,15 +3163,15 @@
       <c r="Y19" s="26"/>
       <c r="Z19" s="32">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="AA19" s="27">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="27" t="str">
         <f>IFERROR(VLOOKUP(A19,Plan2!$A$1:$F$777,6,0),"-")</f>
-        <v>78</v>
-      </c>
-      <c r="AB19" s="28">
+        <v>-</v>
+      </c>
+      <c r="AB19" s="28" t="str">
         <f t="shared" si="1"/>
-        <v>312</v>
+        <v>-</v>
       </c>
       <c r="AF19" s="7" t="s">
         <v>55</v>
@@ -3243,9 +3179,7 @@
       <c r="AG19" s="33"/>
     </row>
     <row r="20" spans="1:33" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="95">
-        <v>2230</v>
-      </c>
+      <c r="A20" s="95"/>
       <c r="B20" s="98"/>
       <c r="C20" s="98"/>
       <c r="D20" s="98"/>
@@ -3257,18 +3191,10 @@
       <c r="J20" s="98"/>
       <c r="K20" s="98"/>
       <c r="L20" s="44"/>
-      <c r="M20" s="48">
-        <v>2</v>
-      </c>
-      <c r="N20" s="36">
-        <v>2</v>
-      </c>
-      <c r="O20" s="36">
-        <v>2</v>
-      </c>
-      <c r="P20" s="36">
-        <v>2</v>
-      </c>
+      <c r="M20" s="48"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
       <c r="Q20" s="36"/>
       <c r="R20" s="36"/>
       <c r="S20" s="36"/>
@@ -3280,15 +3206,15 @@
       <c r="Y20" s="26"/>
       <c r="Z20" s="32">
         <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="AA20" s="27">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="27" t="str">
         <f>IFERROR(VLOOKUP(A20,Plan2!$A$1:$F$777,6,0),"-")</f>
-        <v>84.9</v>
-      </c>
-      <c r="AB20" s="28">
+        <v>-</v>
+      </c>
+      <c r="AB20" s="28" t="str">
         <f t="shared" si="1"/>
-        <v>679.2</v>
+        <v>-</v>
       </c>
       <c r="AF20" s="7">
         <v>91</v>
@@ -4359,14 +4285,14 @@
       <c r="Y45" s="30"/>
       <c r="Z45" s="31">
         <f>SUM(Z13:Z44)</f>
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="AA45" s="53" t="s">
         <v>148</v>
       </c>
       <c r="AB45" s="54">
         <f>SUM(AB13:AB44)</f>
-        <v>3817.8</v>
+        <v>0</v>
       </c>
       <c r="AC45" s="21"/>
       <c r="AF45" s="8">
@@ -4405,7 +4331,7 @@
         <v>149</v>
       </c>
       <c r="AB46" s="70">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="AC46" s="55"/>
       <c r="AF46" s="8" t="s">
@@ -4445,7 +4371,7 @@
       </c>
       <c r="AB47" s="56">
         <f>AB45*AB46</f>
-        <v>458.13600000000002</v>
+        <v>0</v>
       </c>
       <c r="AC47" s="55"/>
       <c r="AF47" s="8">
@@ -4485,7 +4411,7 @@
       </c>
       <c r="AB48" s="139">
         <f>AB45-AB47</f>
-        <v>3359.6640000000002</v>
+        <v>0</v>
       </c>
       <c r="AC48" s="21"/>
       <c r="AF48" s="8" t="s">
@@ -7210,7 +7136,7 @@
       <c r="D78" s="34"/>
       <c r="E78" s="35"/>
       <c r="F78" s="88">
-        <v>133.9</v>
+        <v>134.9</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
@@ -7234,7 +7160,7 @@
       <c r="D80" s="34"/>
       <c r="E80" s="35"/>
       <c r="F80" s="88">
-        <v>111.9</v>
+        <v>112.9</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
@@ -7366,7 +7292,7 @@
       <c r="D91" s="34"/>
       <c r="E91" s="35"/>
       <c r="F91" s="88">
-        <v>98.8</v>
+        <v>98.9</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
@@ -8196,7 +8122,7 @@
       <c r="D160" s="34"/>
       <c r="E160" s="35"/>
       <c r="F160" s="88">
-        <v>92.9</v>
+        <v>91.9</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.2">
@@ -8328,7 +8254,7 @@
       <c r="D171" s="34"/>
       <c r="E171" s="35"/>
       <c r="F171" s="88">
-        <v>59.9</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.2">
@@ -8340,7 +8266,7 @@
       <c r="D172" s="34"/>
       <c r="E172" s="35"/>
       <c r="F172" s="88">
-        <v>62.9</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.2">
@@ -8544,7 +8470,7 @@
       <c r="D189" s="34"/>
       <c r="E189" s="35"/>
       <c r="F189" s="88">
-        <v>60.5</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.2">
@@ -21881,7 +21807,7 @@
       <c r="F2784" s="91"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="3kEDw3lOXuwI7BvP7C4Zi5aItLxtd7US1hYJC8b14elQ1LmV6yHY3mHAJUMVqg/Q+PewRZknBQfTgTnwXhyGmA==" saltValue="drzZi0z8zr7Kjlwli5pRxg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="PWSuG257p6n8lbhUwiF4tw0Pw118H58kN5D1kMLelOjlvh7tk+DHXUlR9/bt9DIwckwntPls3dJdsuZWT849lA==" saltValue="zLUyB87KH77CUOpfqGU80w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <sortState ref="A2:B231">
     <sortCondition ref="A1"/>
   </sortState>
